--- a/data/tags/סינגלים חדשים/global/2026-01-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:L61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -413,7 +413,7 @@
         <v>תאריך סריקה</v>
       </c>
       <c r="E1" t="str">
-        <v>תיאור</v>
+        <v>שעה</v>
       </c>
       <c r="F1" t="str">
         <v>משך</v>
@@ -442,7 +442,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409328&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409328&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-22</v>
@@ -457,15 +457,18 @@
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
       </c>
       <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
         <v>שמואל חי מעודה - ארוממך להורדה</v>
       </c>
     </row>
@@ -477,7 +480,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409327&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409327&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-22</v>
@@ -492,15 +495,18 @@
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
       </c>
       <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
         <v>שירה זלוף - לא אוהבת סרטים להורדה</v>
       </c>
     </row>
@@ -512,7 +518,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409326&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409326&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-22</v>
@@ -527,15 +533,18 @@
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J4" t="str">
         <v/>
       </c>
       <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
         <v>שי נחייסי - הלב שלם להורדה</v>
       </c>
     </row>
@@ -547,7 +556,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409325&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409325&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-22</v>
@@ -562,15 +571,18 @@
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J5" t="str">
         <v/>
       </c>
       <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
         <v>שובל בבייב - כמו ציפור להורדה</v>
       </c>
     </row>
@@ -582,7 +594,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409324&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409324&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-22</v>
@@ -597,15 +609,18 @@
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J6" t="str">
         <v/>
       </c>
       <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
         <v>רן דנקר - תמונת מצב להורדה</v>
       </c>
     </row>
@@ -617,7 +632,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409323&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409323&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-22</v>
@@ -632,15 +647,18 @@
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J7" t="str">
         <v/>
       </c>
       <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
         <v>פייגה סבג - שוב לבד להורדה</v>
       </c>
     </row>
@@ -652,7 +670,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409322&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409322&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-22</v>
@@ -667,15 +685,18 @@
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J8" t="str">
         <v/>
       </c>
       <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
         <v>פארידה - מחרוזת פארידה 2026 להורדה</v>
       </c>
     </row>
@@ -687,7 +708,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409321&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409321&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-22</v>
@@ -702,15 +723,18 @@
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J9" t="str">
         <v/>
       </c>
       <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
         <v>נתי קוריטרו - תחנה בזמן להורדה</v>
       </c>
     </row>
@@ -722,7 +746,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409320&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409320&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-22</v>
@@ -737,15 +761,18 @@
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J10" t="str">
         <v/>
       </c>
       <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
         <v>מושיקו מזרחי - כמו בחלום להורדה</v>
       </c>
     </row>
@@ -757,7 +784,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409319&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409319&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-22</v>
@@ -772,15 +799,18 @@
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J11" t="str">
         <v/>
       </c>
       <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
         <v>מושיקו מזרחי - זמר בפאן להורדה</v>
       </c>
     </row>
@@ -792,7 +822,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409318&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409318&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-22</v>
@@ -807,15 +837,18 @@
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I12" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J12" t="str">
         <v/>
       </c>
       <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
         <v>מושיקו מזרחי - הכל מכתוב להורדה</v>
       </c>
     </row>
@@ -827,7 +860,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409317&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409317&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-22</v>
@@ -842,15 +875,18 @@
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I13" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J13" t="str">
         <v/>
       </c>
       <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
         <v>יניב מדר - להילולה קאבר להורדה</v>
       </c>
     </row>
@@ -862,7 +898,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409316&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409316&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-22</v>
@@ -877,15 +913,18 @@
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I14" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J14" t="str">
         <v/>
       </c>
       <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
         <v>יואב זלדין - טייס חופשי להורדה</v>
       </c>
     </row>
@@ -897,7 +936,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409315&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409315&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-22</v>
@@ -912,15 +951,18 @@
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I15" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J15" t="str">
         <v/>
       </c>
       <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
         <v>יגל יובל שרעבי - שקרן מוסמך להורדה</v>
       </c>
     </row>
@@ -932,7 +974,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409314&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409314&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-22</v>
@@ -947,15 +989,18 @@
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I16" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J16" t="str">
         <v/>
       </c>
       <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
         <v>דה לוי - אול אין להורדה</v>
       </c>
     </row>
@@ -967,7 +1012,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409313&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409313&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-22</v>
@@ -982,15 +1027,18 @@
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J17" t="str">
         <v/>
       </c>
       <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
         <v>גל טייב - לפני הזריחה להורדה</v>
       </c>
     </row>
@@ -1002,7 +1050,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409312&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409312&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-22</v>
@@ -1017,15 +1065,18 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I18" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J18" t="str">
         <v/>
       </c>
       <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
         <v>גיא בן שמעון - אני מפחד וזה בסדר להורדה</v>
       </c>
     </row>
@@ -1037,7 +1088,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409311&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409311&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-22</v>
@@ -1052,15 +1103,18 @@
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I19" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J19" t="str">
         <v/>
       </c>
       <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
         <v>אמיר שדה - גופיית כדורסל להורדה</v>
       </c>
     </row>
@@ -1072,7 +1126,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409310&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409310&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-22</v>
@@ -1087,15 +1141,18 @@
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I20" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J20" t="str">
         <v/>
       </c>
       <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
         <v>אלמוג זגרון - מה זה בית להורדה</v>
       </c>
     </row>
@@ -1107,7 +1164,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409309&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409309&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-22</v>
@@ -1122,15 +1179,18 @@
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I21" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J21" t="str">
         <v/>
       </c>
       <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
         <v>אוריה - להיות באמת להורדה</v>
       </c>
     </row>
@@ -1142,7 +1202,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409308&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409308&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-22</v>
@@ -1157,15 +1217,18 @@
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I22" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J22" t="str">
         <v/>
       </c>
       <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
         <v>אבי ריימי &amp; יאיר בודנר מארחים את אברימי רוט - מִזְמוֹר שִׁיר</v>
       </c>
     </row>
@@ -1177,7 +1240,7 @@
         <v>2026-01-21</v>
       </c>
       <c r="C23" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409307&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409307&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-22</v>
@@ -1192,15 +1255,18 @@
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I23" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J23" t="str">
         <v/>
       </c>
       <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
         <v>שירז לביא - נראה לי זה הסוף להורדה</v>
       </c>
     </row>
@@ -1212,7 +1278,7 @@
         <v>2026-01-21</v>
       </c>
       <c r="C24" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409306&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409306&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-22</v>
@@ -1227,15 +1293,18 @@
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I24" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J24" t="str">
         <v/>
       </c>
       <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
         <v>ראובן המלאך - תגידי מה עובר עלייך להורדה</v>
       </c>
     </row>
@@ -1247,7 +1316,7 @@
         <v>2026-01-21</v>
       </c>
       <c r="C25" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409305&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409305&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-22</v>
@@ -1262,15 +1331,18 @@
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I25" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J25" t="str">
         <v/>
       </c>
       <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
         <v>עידו ביטון - היום יוצאים להורדה</v>
       </c>
     </row>
@@ -1282,7 +1354,7 @@
         <v>2026-01-21</v>
       </c>
       <c r="C26" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409304&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409304&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-22</v>
@@ -1297,15 +1369,18 @@
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I26" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J26" t="str">
         <v/>
       </c>
       <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
         <v>מור זיו - השער נפתח להורדה</v>
       </c>
     </row>
@@ -1317,7 +1392,7 @@
         <v>2026-01-21</v>
       </c>
       <c r="C27" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409303&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409303&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-22</v>
@@ -1332,15 +1407,18 @@
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I27" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J27" t="str">
         <v/>
       </c>
       <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
         <v>ישראל סוסנה וחברים - מחרוזת ראש חודש שמח 2026 להורדה</v>
       </c>
     </row>
@@ -1352,7 +1430,7 @@
         <v>2026-01-21</v>
       </c>
       <c r="C28" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409302&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409302&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-22</v>
@@ -1367,15 +1445,18 @@
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I28" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J28" t="str">
         <v/>
       </c>
       <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
         <v>הרצף הגנטי מארח את אלעד עמדי - חוזר אל הדרכים להורדה</v>
       </c>
     </row>
@@ -1387,7 +1468,7 @@
         <v>2026-01-21</v>
       </c>
       <c r="C29" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409301&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409301&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-22</v>
@@ -1402,15 +1483,18 @@
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I29" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J29" t="str">
         <v/>
       </c>
       <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
         <v>ג'ולייטה - מי יציל אותי להורדה</v>
       </c>
     </row>
@@ -1422,7 +1506,7 @@
         <v>2026-01-21</v>
       </c>
       <c r="C30" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409300&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409300&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-22</v>
@@ -1437,15 +1521,18 @@
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I30" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J30" t="str">
         <v/>
       </c>
       <c r="K30" t="str">
+        <v/>
+      </c>
+      <c r="L30" t="str">
         <v>אמיתי צדוק - במנורה אני נשבע להורדה</v>
       </c>
     </row>
@@ -1457,7 +1544,7 @@
         <v>2026-01-21</v>
       </c>
       <c r="C31" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409299&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409299&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-22</v>
@@ -1472,15 +1559,18 @@
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I31" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J31" t="str">
         <v/>
       </c>
       <c r="K31" t="str">
+        <v/>
+      </c>
+      <c r="L31" t="str">
         <v>איתי דלומי - שיר היונה להורדה</v>
       </c>
     </row>
@@ -1498,24 +1588,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
         <v>רן דנקר שר שיר וידויי שמנסח מצוקה מודרנית בשפה ישירה, זהירה ומודעת לעצמה. “תמונת מצב” אינו שיר משבר קיצוני אלא שיר על שחיקה מתמשכת. זהו תיעוד של חיים תחת לחץ: ציפיות, תדמית, עבודה רגשית בלתי פוסקת, והפחד ש “יעלו עליי”</v>
       </c>
-      <c r="F32" t="str">
-        <v/>
-      </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I32" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J32" t="str">
         <v/>
       </c>
       <c r="K32" t="str">
+        <v/>
+      </c>
+      <c r="L32" t="str">
         <v>רן דנקר – תמונת מצב</v>
       </c>
     </row>
@@ -1533,24 +1626,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
         <v>תמר כהנא שרה בלדת פופ מודעת לעצמה, שנעה מוזיקלית במרכז המפה ומטעינה אותה במשמעות רגשית ומטאפורית. זהו שיר שאומר: לא כל גל צריך להפיל אותך, לפעמים צריך רק מישהו שיזכיר לך מי את באמת. הדימוי המרכזי של השיר – “הוא</v>
       </c>
-      <c r="F33" t="str">
-        <v/>
-      </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I33" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J33" t="str">
         <v/>
       </c>
       <c r="K33" t="str">
+        <v/>
+      </c>
+      <c r="L33" t="str">
         <v>תמר כהנא – את הים</v>
       </c>
     </row>
@@ -1568,24 +1664,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
         <v>"הולכת אחורה” של אמונה מחפוד הוא שיר שממוקם על התפר שבין פופ רגיש ואינטימי ובין ראפ דיבורי וחשוף בעיבוד פונקציונלי חכם עם גרוב פאנקי. זהו שיר שלא מנסה להרשים בכוח, אלא לספר אמת רגשית מורכבת, בקול נשי מודע לעצמו, פגיע</v>
       </c>
-      <c r="F34" t="str">
-        <v/>
-      </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I34" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J34" t="str">
         <v/>
       </c>
       <c r="K34" t="str">
+        <v/>
+      </c>
+      <c r="L34" t="str">
         <v>אמונה מחפוד – הולכת אחורה</v>
       </c>
     </row>
@@ -1603,24 +1702,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
         <v>קובי אפללו שר "שראל”, פופ ים־תיכוני מלודי, נגיש  מנחם-מאחד.  אפללו בחר באסטרטגיה ברורה: האנשה של המדינה/העם בדמות אדם בשם “ישראל”, וכך להפוך סיפור לאומי־פוליטי לנרטיב רגשי־אישי. זו בחירה מוכרת בפופ הישראלי, אך כזו שעדיין עובדת כשהיא מבוצעת בכנות ובהתכוונות. הטקסט</v>
       </c>
-      <c r="F35" t="str">
-        <v/>
-      </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I35" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J35" t="str">
         <v/>
       </c>
       <c r="K35" t="str">
+        <v/>
+      </c>
+      <c r="L35" t="str">
         <v>קובי אפללו – ישראל</v>
       </c>
     </row>
@@ -1638,24 +1740,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
         <v>זהו שיר פופ קצבי, מלוטש ומיידי, שממוקם בבירור בתוך המיינסטרים של הפופ־המזרחי העכשווי. הוא עשוי היטב ברמה ההפקתית, אך סובל מתחושת דז׳ה־וו חזקה – הן מוזיקלית והן טקסטואלית. דניאל ג'מל (דה וויס 5) חוזר עם טקסט העוסק בפרידה לא סימטרית:</v>
       </c>
-      <c r="F36" t="str">
-        <v/>
-      </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I36" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J36" t="str">
         <v/>
       </c>
       <c r="K36" t="str">
+        <v/>
+      </c>
+      <c r="L36" t="str">
         <v>דניאל ג'מל – יוצאת מהקצב</v>
       </c>
     </row>
@@ -1673,24 +1778,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
         <v>אודי תורג'מן ומיקה קרני פותחים את השיר בבית האחרון של הפואמה: “נתתי לך שעון במקוםטבעת נישואיןזמן עגול וטובשל נדודי שינה ונצח” הבית הזה הוא  תמצית של קשר שהומר מאידיליה רגשית לסמל מופשט של זמן, החמצה ונצח סדוק. כשהוא מוצב בפתיחה.</v>
       </c>
-      <c r="F37" t="str">
-        <v/>
-      </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I37" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J37" t="str">
         <v/>
       </c>
       <c r="K37" t="str">
+        <v/>
+      </c>
+      <c r="L37" t="str">
         <v>מיקה קרני ואודי תורג'מן – כמו שהיה</v>
       </c>
     </row>
@@ -1708,24 +1816,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
         <v>אביעד הנדל מנסה להמחיש אווירה בשיר בקול רך מהורהר, לחן מינורי אפלולי בשיר סוריאליסטי.  הטקסט מתאר פכפוך, ציוץ ציפורים, צוקים וים – דימויים חזותיים ואוויריים. המוזיקה המינורית משקפת את ההרהור והספק של השאלות (“האם הדרך היא סלעית? האם כבושה?”). היא</v>
       </c>
-      <c r="F38" t="str">
-        <v/>
-      </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I38" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J38" t="str">
         <v/>
       </c>
       <c r="K38" t="str">
+        <v/>
+      </c>
+      <c r="L38" t="str">
         <v>אביעד הנדל – טורקיז</v>
       </c>
     </row>
@@ -1743,24 +1854,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
         <v>ג’ונו ויין (יונתן ויינרייך) שר בלדה רכה, אינטימית ומדויקת, שמצליחה לתאר תנועה בתוך קשר בלי דרמה מוחצנת, אלא דרך סדקים קטנים, מרחקים דקים וסאונד מחושב. כבר משם השיר ברור שלא מדובר בבריחה או ניתוק, אלא במצב תודעתי בתוך מערכת יחסים.</v>
       </c>
-      <c r="F39" t="str">
-        <v/>
-      </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I39" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J39" t="str">
         <v/>
       </c>
       <c r="K39" t="str">
+        <v/>
+      </c>
+      <c r="L39" t="str">
         <v>Juno Vine – Space</v>
       </c>
     </row>
@@ -1778,24 +1892,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
         <v>שירה של דליה רביקוביץ, בלחן המקורי של מלכה שפיגל וקולין ניומן (1993), ובביצוע המחודש של רונית שחר וקרני פוסטל הוא קאבר שמעמיק את האינטימיות והעדינות של הטקסט דרך עיבוד מינימליסטי לגיטרות חשמליות וכלי מיתר אקוסטיים. שני קולות נשיים שרים טקסט</v>
       </c>
-      <c r="F40" t="str">
-        <v/>
-      </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I40" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J40" t="str">
         <v/>
       </c>
       <c r="K40" t="str">
+        <v/>
+      </c>
+      <c r="L40" t="str">
         <v>רונית שחר וקרני פוסטל – כישופים</v>
       </c>
     </row>
@@ -1813,24 +1930,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
         <v>גל ניסמן שר בקול חשוף, נוגה וכואב בלדת אהבה. השיר נטוע עמוק בהווה – הפיד, מסכים, צילום מסך הלב כדי לשדר כמיהה. הדובר לא משתמש בדימויים הדיגיטליים כדי להקטין את הרגש, אלא כדי להודות שהוא חסר אמצעים מולו. המשפט החוזר</v>
       </c>
-      <c r="F41" t="str">
-        <v/>
-      </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I41" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J41" t="str">
         <v/>
       </c>
       <c r="K41" t="str">
+        <v/>
+      </c>
+      <c r="L41" t="str">
         <v>פול טראנק – אין מילים איתך</v>
       </c>
     </row>
@@ -1848,24 +1968,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
         <v>זהו שיר מינורי, אפלולי ומודע לעצמו, שמצליח להיות אינטימי ופילוסופי בלי להתנשא. הילה רוח מציבה עימות בין הצורך האנושי בסגירה, סדר והיגיון לבין קשר שלא מציית לחוקים. ה”טבע” כאן אינו יער או נוף  אלא כוח בלתי נשלט: משיכה, כבידה, חזרתיות</v>
       </c>
-      <c r="F42" t="str">
-        <v/>
-      </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I42" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J42" t="str">
         <v/>
       </c>
       <c r="K42" t="str">
+        <v/>
+      </c>
+      <c r="L42" t="str">
         <v>הילה רוח – טבע</v>
       </c>
     </row>
@@ -1883,24 +2006,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
         <v>"מלאך” של יובל רונן הוא שיר התבגרות רגשית במסווה של סיפור אגדי. זהו שיר על אהבה חדשה שמופיעה ברגע של שבר פנימי, ומציעה לא גאולה מלאה – אלא הפוגה. המעבר המוזיקלי משירה כמעט מלוחשת לקצב ואלס אינו רק אמצעי מוזיקלי,</v>
       </c>
-      <c r="F43" t="str">
-        <v/>
-      </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I43" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J43" t="str">
         <v/>
       </c>
       <c r="K43" t="str">
+        <v/>
+      </c>
+      <c r="L43" t="str">
         <v>יובל רונן – מלאך‎</v>
       </c>
     </row>
@@ -1918,24 +2044,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
         <v>„מפלצת” היא בלדת רוק מלנכולית פנימית איטית, שמתמקדת לא באיום חיצוני אלא בזהות מתפוררת מבפנים. זהו שיר וידוי, כמעט יומן נפשי, שבו הגיטרה החשמלית לא “מובילה” את השיר – אלא נושמת יחד עם הטקסט. המפלצת שבצחי אלוש אינה דימוי פנטסטי,</v>
       </c>
-      <c r="F44" t="str">
-        <v/>
-      </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I44" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J44" t="str">
         <v/>
       </c>
       <c r="K44" t="str">
+        <v/>
+      </c>
+      <c r="L44" t="str">
         <v>צחי אלוש – מפלצת</v>
       </c>
     </row>
@@ -1953,24 +2082,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
         <v>השיר נטוע עמוק בז’אנר פופ ים־תיכוני מיד־טמפו מרומם נפש, כזה שמאפיין תקופות של חיפוש פנימי וקבלת החלטות. זהו שיר של מעבר: בין ספק לאמונה, בין פחד לרוגע, בין פעולה להשלמה. הקצב הבינוני מאפשר לשיר להיות גם מדיטטיבי וגם נגיש לרדיו,</v>
       </c>
-      <c r="F45" t="str">
-        <v/>
-      </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I45" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J45" t="str">
         <v/>
       </c>
       <c r="K45" t="str">
+        <v/>
+      </c>
+      <c r="L45" t="str">
         <v>שניר עזרן – אין מה לדאוג</v>
       </c>
     </row>
@@ -1988,24 +2120,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
         <v>"לב לבן” של שולי רנד הוא שיר אהבה שיש בו רוך, אבל גם הכרעה. אהבה כאן היא לא מפלט מהעולם, אלא דרך להיות בו אחרת. זהו שיר קבלה לא של רגע שיא רומנטי, אלא של הגעה אחרי דרך ארוכה, יבשה,</v>
       </c>
-      <c r="F46" t="str">
-        <v/>
-      </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I46" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J46" t="str">
         <v/>
       </c>
       <c r="K46" t="str">
+        <v/>
+      </c>
+      <c r="L46" t="str">
         <v>שולי רנד – לב לבן</v>
       </c>
     </row>
@@ -2023,24 +2158,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
         <v>"הארץ המובטחת” של דודי בר-דוד משתמש בקצב נסיעה כאלגוריה לחיפוש זהות ישראלית־אישית: בן מול אב, עבר מול עתיד, אמונה מול ריק. זה שיר של נוסע קדימה, אבל כל הזמן מסתכל במראה. כבר מהשורה הראשונה ברור שזה שיר דרך – אבל</v>
       </c>
-      <c r="F47" t="str">
-        <v/>
-      </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I47" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J47" t="str">
         <v/>
       </c>
       <c r="K47" t="str">
+        <v/>
+      </c>
+      <c r="L47" t="str">
         <v>דודי בר דוד – הארץ המובטחת</v>
       </c>
     </row>
@@ -2058,24 +2196,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
         <v>זה שיר חזק, מטא-מוזיקלי, וכואב, ובעיקר כזה שמדבר מתוך הסצנה הישראלית אל עצמה. ״תחזור לנגן בס״ הוא הרבה יותר מהוראה טכנית: זה שיר על זהות, אובדן דרך, ועל הצלה דרך מוזיקה. זה שיר דרמטי־וידויי של שלום גד, שבו ערן צור</v>
       </c>
-      <c r="F48" t="str">
-        <v/>
-      </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I48" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J48" t="str">
         <v/>
       </c>
       <c r="K48" t="str">
+        <v/>
+      </c>
+      <c r="L48" t="str">
         <v>שלום גד וערן צור – תחזור לנגן בס</v>
       </c>
     </row>
@@ -2093,24 +2234,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
         <v>הפשטות היא הכוח. זה שיר שנשמע כמו משהו שתמיד היה כאן, גם אם הוא חדש. "האחיות" – זוהר גינזבורג, טולה בן ארי, מיקה שדה שרות שיר פולק בסגנון אולד סקול , לא וידוי אישי, לא סיפור פרטי, אלא קריאה. הזמנה</v>
       </c>
-      <c r="F49" t="str">
-        <v/>
-      </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I49" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J49" t="str">
         <v/>
       </c>
       <c r="K49" t="str">
+        <v/>
+      </c>
+      <c r="L49" t="str">
         <v>האחיות – בואו איתי</v>
       </c>
     </row>
@@ -2128,24 +2272,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
         <v>"כמה שלא ניסיתי” הוא שיר פופ רומנטי טהור על אהבה ראשונה שלא קורית. לא דרמה גדולה, לא שברון לב טראגי  אלא אכזבה מתוקה־מרירה, כזו שכולנו מכירים מהגיל שבו הרגש גדול מהכלים שיש לנו להתמודד איתו. כבר בבית הראשון אנחנו בתוך</v>
       </c>
-      <c r="F50" t="str">
-        <v/>
-      </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I50" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J50" t="str">
         <v/>
       </c>
       <c r="K50" t="str">
+        <v/>
+      </c>
+      <c r="L50" t="str">
         <v>עידו מלכה – כמה שלא ניסיתי</v>
       </c>
     </row>
@@ -2163,24 +2310,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
         <v>זה לגמרי אמדורסקי במוד שלו – אינטימי, חושני, קצת מנוכר וקצת פגיע. ״עד שירדו דמעות״ מצטייר כשיר תשוקה לילי, כמעט קולנועי, שמתרחש במרחב שבין גוף לנפש. אין כאן סיפור ליניארי, אלא רצף של רגעים, מגעים והבהובים רגשיים. הכול קורה עכשיו,</v>
       </c>
-      <c r="F51" t="str">
-        <v/>
-      </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I51" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J51" t="str">
         <v/>
       </c>
       <c r="K51" t="str">
+        <v/>
+      </c>
+      <c r="L51" t="str">
         <v>אסף אמדורסקי – עד שירדו דמעות</v>
       </c>
     </row>
@@ -2198,24 +2348,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
         <v>המשפט “אני רוצה לשיר” ששרה ליר חוטובלי  לא מדבר על שירה כמטרה בלבדית  שעומדת בפני עצמה. השירה כאן היא דרך לפרוק, דרך להתקרב, דרך להמשיך למרות הכאב, דרך לאהוב. השירה – אמצעי לא מטרה. המלודיה שלה בנויה סימטרית וברורה –</v>
       </c>
-      <c r="F52" t="str">
-        <v/>
-      </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I52" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J52" t="str">
         <v/>
       </c>
       <c r="K52" t="str">
+        <v/>
+      </c>
+      <c r="L52" t="str">
         <v>ליר – אני רוצה לשיר</v>
       </c>
     </row>
@@ -2233,24 +2386,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E53" t="str">
+        <v/>
+      </c>
+      <c r="F53" t="str">
         <v>,הכל יעבור” בדואט אברהם טל וטוהר גדסי הוא שיר שנולד במודע מתוך רגע חברתי־רגשי: שיחת סלון, עייפות מהקיטוב, רצון להרגיע. זה לא שיר שנכתב כפואטיקה צרופה, אלא מתוך מצב. השניים מכוונים לשיר מחבק, אופטימי, מפייס, שיר שמניח פלסטר רגשי על</v>
       </c>
-      <c r="F53" t="str">
-        <v/>
-      </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I53" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J53" t="str">
         <v/>
       </c>
       <c r="K53" t="str">
+        <v/>
+      </c>
+      <c r="L53" t="str">
         <v>אברהם טל וטוהר גדסי – הכל יעבור</v>
       </c>
     </row>
@@ -2268,24 +2424,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
         <v>“אמצע העולם” של בן שוקרון הוא בלדת־דרך ישראלית, כזו שנעה על קצב מידטמפו יציב, כמו נסיעה ארוכה בכביש מוכר- לא ממהרת, לא בורחת, פשוט ממשיכה. הפתיחה – “שביל קטן באמצע העולם” היא הצהרה זהותית חזקה: המקום קטן, אולי שולי על</v>
       </c>
-      <c r="F54" t="str">
-        <v/>
-      </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I54" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J54" t="str">
         <v/>
       </c>
       <c r="K54" t="str">
+        <v/>
+      </c>
+      <c r="L54" t="str">
         <v>בן שוקרון – אמצע העולם</v>
       </c>
     </row>
@@ -2303,24 +2462,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
         <v>דרך אנרגיה רוקית, שפה חצופה ומודעות עצמית חדה, סטלה מושאילוב שרה שיר אישי מאוד וגם מספיק חד כדי שמי ששומעת אותה ירגיש שהוא נכתב עליה. הבלרינה כאן היא הציפייה להיות עדינה, ממושמעת, יפה במובן המאולף, וכשהיא אומרת: – “אני אף</v>
       </c>
-      <c r="F55" t="str">
-        <v/>
-      </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I55" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J55" t="str">
         <v/>
       </c>
       <c r="K55" t="str">
+        <v/>
+      </c>
+      <c r="L55" t="str">
         <v>סטלה – בלרינה</v>
       </c>
     </row>
@@ -2338,24 +2500,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
         <v>יערה לוי שרה שרה את שברון ליבה על מערכת יחסים מורכבת בין בני זוג, מנקודת מבטה של מישהי שעייפה רגשית. על משיכה לצד תסכול, על ניסיונות שלא נגמרים, על חיפוש אחרי משהו אמיתי- ועל הרגע שבו כבר אין כוח להתחיל</v>
       </c>
-      <c r="F56" t="str">
-        <v/>
-      </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I56" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J56" t="str">
         <v/>
       </c>
       <c r="K56" t="str">
+        <v/>
+      </c>
+      <c r="L56" t="str">
         <v>יערה לוי – מתי זה יפסק</v>
       </c>
     </row>
@@ -2373,24 +2538,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
         <v>זה שיר שמבקש לא לצעוק כאב – אלא להודות בו בכאב "לא ידעתי שככה הכאב מדבר/ אולי יכולתי יותר/ אולי יכולתי יותר/ אולי יכולתי יותר". נינט שרה באזור גבוה יחסית, אבל בלי כוחנות, בלי “שואו”, עם תחושת ריחוף שברירי. זה</v>
       </c>
-      <c r="F57" t="str">
-        <v/>
-      </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I57" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J57" t="str">
         <v/>
       </c>
       <c r="K57" t="str">
+        <v/>
+      </c>
+      <c r="L57" t="str">
         <v>נינט טייב – אולי יכולתי יותר</v>
       </c>
     </row>
@@ -2408,24 +2576,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
         <v>שיר לוי שר בלדה שמתחילה מהאדמה, עוברת דרך שבר, ומרימה את הראש אל איזו נקודת אור.המסע בשיר אינו ליניארי. אין “עברתי את זה”. להפך: "שוב נכשל ושוב נופל/ אז אני קם ומתפלל” זהו מסע של מצבים חוזרים: נפילה, תפילה, אחיזה</v>
       </c>
-      <c r="F58" t="str">
-        <v/>
-      </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I58" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J58" t="str">
         <v/>
       </c>
       <c r="K58" t="str">
+        <v/>
+      </c>
+      <c r="L58" t="str">
         <v>שיר לוי – רחוב ללא מוצא</v>
       </c>
     </row>
@@ -2443,24 +2614,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
         <v>העובדה שענת מושקובסקי שרה מנקודת מבט של גבר אינה גימיק – היא חלק מהאמירה והסיפור. הוא (הדובר)  אינו מאשים אותה בקול רם, לא מציג עצמו כגיבור ולא מתמסכן באופן מוחצן. זה גבר פסיבי יחסית, מתבונן בעצמו דרך העזיבה שלה, תקוע</v>
       </c>
-      <c r="F59" t="str">
-        <v/>
-      </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I59" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J59" t="str">
         <v/>
       </c>
       <c r="K59" t="str">
+        <v/>
+      </c>
+      <c r="L59" t="str">
         <v>ענת מושקובסקי – דינה</v>
       </c>
     </row>
@@ -2478,24 +2652,27 @@
         <v>2026-01-22</v>
       </c>
       <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
         <v>אופירה שופן שרה בטון: שטוח יחסית, מאופק רגשית, כמעט אדיש במכוון על יחסים עקרים. גם כשהטקסט מדבר על כמיהה, בלבול ורצון – הקול לא מתרגש. הפער הזה יוצר תחושה של רגש קיים, אבל חסר כוח להתפרץ. זה תואם את הדמות</v>
       </c>
-      <c r="F60" t="str">
-        <v/>
-      </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I60" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J60" t="str">
         <v/>
       </c>
       <c r="K60" t="str">
+        <v/>
+      </c>
+      <c r="L60" t="str">
         <v>אופירה שופן – בא לי</v>
       </c>
     </row>
@@ -2513,30 +2690,33 @@
         <v>2026-01-22</v>
       </c>
       <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
         <v>אינטימית נוגה, רגישה ומרוגשת, בליווי פסנתר מינימליסטי, ירונה כספי שרה יחסי קרבה כמצב נפשי ולא רק פיזי. ליבת השיר היא רעיון הקרבה לא כאקט דרמטי או תשוקתי, אלא כמצב שקט, מתמשך, כמעט מדיטטיבי. הדובר אינו מתאר רגע שיא אלא שהייה-</v>
       </c>
-      <c r="F61" t="str">
-        <v/>
-      </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I61" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J61" t="str">
         <v/>
       </c>
       <c r="K61" t="str">
+        <v/>
+      </c>
+      <c r="L61" t="str">
         <v>ירונה כספי – קרבה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L61"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-01-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-01-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>הארי סטיילס Aperture</v>
+        <v>רייצ'ל – שווה לנסיון</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-24</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%90%d7%a8%d7%99-%d7%a1%d7%98%d7%99%d7%99%d7%9c%d7%a1-aperture/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%99%d7%99%d7%a6%d7%9c-%d7%a9%d7%95%d7%95%d7%94-%d7%9c%d7%a0%d7%a1%d7%99%d7%95%d7%9f/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-24</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>אחרי של שישה פרסי Brit, שלושה פרסי גראמי ושבעה סינגלים בטופ 10 הבריטי, ניתן לומר בביטחון שהארי סטיילס הצליח לעקוף באלגנטיות את המהמורות שחוסמות את הדרך אחרי שהיית חבר בלהקת בנים. Aperture הוא הסינגל הראשון מאלבומו הרביעי  בעל השם המבלבל</v>
+        <v>"שווה לניסיון“ ששרה רייצ'ל אטיאס הוא שיר דאנס קצבי עם טקסט קיומי־ביקורתי. המציג פער מכוון בין מוזיקה קליטה, תזזיתית, כמעט חגיגית לבין מילים האומרות  ציניות, אובדות אמון. “כולנו מאבדים איזון” הוא המשפט המרכזי – והוא חוזר שוב ושוב.  האם מדובר</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>הארי סטיילס Aperture</v>
+        <v>רייצ'ל – שווה לנסיון</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-01-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,45 +436,2287 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>ראובן המלאך - תגידי מה עובר עלייך</v>
+      </c>
+      <c r="B2" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="C2" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409306&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+      </c>
+      <c r="D2" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
+        <v>ראובן המלאך - תגידי מה עובר עלייך</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>שמואל חי מעודה - ארוממך</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409328&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>שמואל חי מעודה - ארוממך</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>שירה זלוף - לא אוהבת סרטים</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409327&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>שירה זלוף - לא אוהבת סרטים</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>שי נחייסי - הלב שלם</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409326&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>שי נחייסי - הלב שלם</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>שובל בבייב - כמו ציפור</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409325&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>שובל בבייב - כמו ציפור</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>רן דנקר - תמונת מצב</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409324&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>רן דנקר - תמונת מצב</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>פייגה סבג - שוב לבד</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409323&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>פייגה סבג - שוב לבד</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>פארידה - מחרוזת פארידה 2026</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409322&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>פארידה - מחרוזת פארידה 2026</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>נתי קוריטרו - תחנה בזמן</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409321&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>נתי קוריטרו - תחנה בזמן</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>מושיקו מזרחי - כמו בחלום</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409320&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>מושיקו מזרחי - כמו בחלום</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>מושיקו מזרחי - זמר בפאן</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409319&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>מושיקו מזרחי - זמר בפאן</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>מושיקו מזרחי - הכל מכתוב</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409318&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>מושיקו מזרחי - הכל מכתוב</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>יניב מדר - להילולה קאבר</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409317&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>יניב מדר - להילולה קאבר</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>יואב זלדין - טייס חופשי</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409316&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>יואב זלדין - טייס חופשי</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>יגל יובל שרעבי - שקרן מוסמך</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409315&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>יגל יובל שרעבי - שקרן מוסמך</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>דה לוי - אול אין</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="C17" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409314&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>דה לוי - אול אין</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>גל טייב - לפני הזריחה</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="C18" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409313&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v>גל טייב - לפני הזריחה</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>גיא בן שמעון - אני מפחד וזה בסדר</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="C19" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409312&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+      </c>
+      <c r="D19" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v>גיא בן שמעון - אני מפחד וזה בסדר</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>אמיר שדה - גופיית כדורסל</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="C20" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409311&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+      </c>
+      <c r="D20" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v>אמיר שדה - גופיית כדורסל</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>אלמוג זגרון - מה זה בית</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="C21" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409310&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+      </c>
+      <c r="D21" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v>אלמוג זגרון - מה זה בית</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>אוריה - להיות באמת</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="C22" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409309&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+      </c>
+      <c r="D22" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v>אוריה - להיות באמת</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>אבי ריימי &amp; יאיר בודנר מארחים את אברימי רוט - מִזְמוֹר שִׁיר</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="C23" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409308&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+      </c>
+      <c r="D23" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v>אבי ריימי &amp; יאיר בודנר מארחים את אברימי רוט - מִזְמוֹר שִׁיר</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>שירז לביא - נראה לי זה הסוף</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2026-01-21</v>
+      </c>
+      <c r="C24" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409307&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+      </c>
+      <c r="D24" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v>שירז לביא - נראה לי זה הסוף</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>עידו ביטון - היום יוצאים</v>
+      </c>
+      <c r="B25" t="str">
+        <v>2026-01-21</v>
+      </c>
+      <c r="C25" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409305&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+      </c>
+      <c r="D25" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <v>עידו ביטון - היום יוצאים</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>מור זיו - השער נפתח</v>
+      </c>
+      <c r="B26" t="str">
+        <v>2026-01-21</v>
+      </c>
+      <c r="C26" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409304&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+      </c>
+      <c r="D26" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <v>מור זיו - השער נפתח</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>ישראל סוסנה וחברים - מחרוזת ראש חודש שמח 2026</v>
+      </c>
+      <c r="B27" t="str">
+        <v>2026-01-21</v>
+      </c>
+      <c r="C27" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409303&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+      </c>
+      <c r="D27" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
+        <v>ישראל סוסנה וחברים - מחרוזת ראש חודש שמח 2026</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>הרצף הגנטי מארח את אלעד עמדי - חוזר אל הדרכים</v>
+      </c>
+      <c r="B28" t="str">
+        <v>2026-01-21</v>
+      </c>
+      <c r="C28" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409302&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+      </c>
+      <c r="D28" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
+        <v>הרצף הגנטי מארח את אלעד עמדי - חוזר אל הדרכים</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>ג'ולייטה - מי יציל אותי</v>
+      </c>
+      <c r="B29" t="str">
+        <v>2026-01-21</v>
+      </c>
+      <c r="C29" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409301&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+      </c>
+      <c r="D29" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
+        <v>ג'ולייטה - מי יציל אותי</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>אמיתי צדוק - במנורה אני נשבע</v>
+      </c>
+      <c r="B30" t="str">
+        <v>2026-01-21</v>
+      </c>
+      <c r="C30" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409300&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+      </c>
+      <c r="D30" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J30" t="str">
+        <v/>
+      </c>
+      <c r="K30" t="str">
+        <v/>
+      </c>
+      <c r="L30" t="str">
+        <v>אמיתי צדוק - במנורה אני נשבע</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>איתי דלומי - שיר היונה</v>
+      </c>
+      <c r="B31" t="str">
+        <v>2026-01-21</v>
+      </c>
+      <c r="C31" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409299&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+      </c>
+      <c r="D31" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J31" t="str">
+        <v/>
+      </c>
+      <c r="K31" t="str">
+        <v/>
+      </c>
+      <c r="L31" t="str">
+        <v>איתי דלומי - שיר היונה</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
         <v>רייצ'ל – שווה לנסיון</v>
       </c>
-      <c r="B2" t="str">
-        <v>2026-01-24</v>
-      </c>
-      <c r="C2" t="str">
+      <c r="B32" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="C32" t="str">
         <v>https://yosmusic.com/%d7%a8%d7%99%d7%99%d7%a6%d7%9c-%d7%a9%d7%95%d7%95%d7%94-%d7%9c%d7%a0%d7%a1%d7%99%d7%95%d7%9f/</v>
       </c>
-      <c r="D2" t="str">
-        <v>2026-01-24</v>
-      </c>
-      <c r="E2" t="str">
-        <v/>
-      </c>
-      <c r="F2" t="str">
+      <c r="D32" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
         <v>"שווה לניסיון“ ששרה רייצ'ל אטיאס הוא שיר דאנס קצבי עם טקסט קיומי־ביקורתי. המציג פער מכוון בין מוזיקה קליטה, תזזיתית, כמעט חגיגית לבין מילים האומרות  ציניות, אובדות אמון. “כולנו מאבדים איזון” הוא המשפט המרכזי – והוא חוזר שוב ושוב.  האם מדובר</v>
       </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
-      <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J2" t="str">
-        <v/>
-      </c>
-      <c r="K2" t="str">
-        <v/>
-      </c>
-      <c r="L2" t="str">
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+      <c r="I32" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J32" t="str">
+        <v/>
+      </c>
+      <c r="K32" t="str">
+        <v/>
+      </c>
+      <c r="L32" t="str">
         <v>רייצ'ל – שווה לנסיון</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>הארי סטיילס Aperture</v>
+      </c>
+      <c r="B33" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="C33" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%90%d7%a8%d7%99-%d7%a1%d7%98%d7%99%d7%99%d7%9c%d7%a1-aperture/</v>
+      </c>
+      <c r="D33" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v>אחרי של שישה פרסי Brit, שלושה פרסי גראמי ושבעה סינגלים בטופ 10 הבריטי, ניתן לומר בביטחון שהארי סטיילס הצליח לעקוף באלגנטיות את המהמורות שחוסמות את הדרך אחרי שהיית חבר בלהקת בנים. Aperture הוא הסינגל הראשון מאלבומו הרביעי  בעל השם המבלבל</v>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+      <c r="I33" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J33" t="str">
+        <v/>
+      </c>
+      <c r="K33" t="str">
+        <v/>
+      </c>
+      <c r="L33" t="str">
+        <v>הארי סטיילס Aperture</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>מאיה בלזיצמן &amp; מתן אפרת – ילדת לב</v>
+      </c>
+      <c r="B34" t="str">
+        <v>2026-01-23</v>
+      </c>
+      <c r="C34" t="str">
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%99%d7%94-%d7%91%d7%9c%d7%96%d7%99%d7%a6%d7%9e%d7%9f-%d7%9e%d7%aa%d7%9f-%d7%90%d7%a4%d7%a8%d7%aa-%d7%99%d7%9c%d7%93%d7%aa-%d7%9c%d7%91/</v>
+      </c>
+      <c r="D34" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v>"ילדת לב” הוא שיר על רגע חמקמק ומבלבל: הזמן שבו ילד מפסיק להיות של ההורה ומתחיל להיות של עצמו. לא מרד דרמטי, לא ניתוק – אלא התרחקות עדינה, כמעט בלתי נראית, שמורגשת דווקא באינטימיות היומיומית:חדר שני, עייפות של הורה, ערב</v>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J34" t="str">
+        <v/>
+      </c>
+      <c r="K34" t="str">
+        <v/>
+      </c>
+      <c r="L34" t="str">
+        <v>מאיה בלזיצמן &amp; מתן אפרת – ילדת לב</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>רן דנקר – תמונת מצב</v>
+      </c>
+      <c r="B35" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="C35" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%9f-%d7%93%d7%a0%d7%a7%d7%a8-%d7%aa%d7%9e%d7%95%d7%a0%d7%aa-%d7%9e%d7%a6%d7%91/</v>
+      </c>
+      <c r="D35" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v>רן דנקר שר שיר וידויי שמנסח מצוקה מודרנית בשפה ישירה, זהירה ומודעת לעצמה. “תמונת מצב” אינו שיר משבר קיצוני אלא שיר על שחיקה מתמשכת. זהו תיעוד של חיים תחת לחץ: ציפיות, תדמית, עבודה רגשית בלתי פוסקת, והפחד ש “יעלו עליי”</v>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+      <c r="I35" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J35" t="str">
+        <v/>
+      </c>
+      <c r="K35" t="str">
+        <v/>
+      </c>
+      <c r="L35" t="str">
+        <v>רן דנקר – תמונת מצב</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>תמר כהנא – את הים</v>
+      </c>
+      <c r="B36" t="str">
+        <v>2026-01-22</v>
+      </c>
+      <c r="C36" t="str">
+        <v>https://yosmusic.com/%d7%aa%d7%9e%d7%a8-%d7%9b%d7%94%d7%a0%d7%90-%d7%90%d7%aa-%d7%94%d7%99%d7%9d/</v>
+      </c>
+      <c r="D36" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v>תמר כהנא שרה בלדת פופ מודעת לעצמה, שנעה מוזיקלית במרכז המפה ומטעינה אותה במשמעות רגשית ומטאפורית. זהו שיר שאומר: לא כל גל צריך להפיל אותך, לפעמים צריך רק מישהו שיזכיר לך מי את באמת. הדימוי המרכזי של השיר – “הוא</v>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+      <c r="I36" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J36" t="str">
+        <v/>
+      </c>
+      <c r="K36" t="str">
+        <v/>
+      </c>
+      <c r="L36" t="str">
+        <v>תמר כהנא – את הים</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>אמונה מחפוד – הולכת אחורה</v>
+      </c>
+      <c r="B37" t="str">
+        <v>2026-01-21</v>
+      </c>
+      <c r="C37" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%9e%d7%95%d7%a0%d7%94-%d7%9e%d7%97%d7%a4%d7%95%d7%93-%d7%94%d7%95%d7%9c%d7%9b%d7%aa-%d7%90%d7%97%d7%95%d7%a8%d7%94/</v>
+      </c>
+      <c r="D37" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v>"הולכת אחורה” של אמונה מחפוד הוא שיר שממוקם על התפר שבין פופ רגיש ואינטימי ובין ראפ דיבורי וחשוף בעיבוד פונקציונלי חכם עם גרוב פאנקי. זהו שיר שלא מנסה להרשים בכוח, אלא לספר אמת רגשית מורכבת, בקול נשי מודע לעצמו, פגיע</v>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J37" t="str">
+        <v/>
+      </c>
+      <c r="K37" t="str">
+        <v/>
+      </c>
+      <c r="L37" t="str">
+        <v>אמונה מחפוד – הולכת אחורה</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>קובי אפללו – ישראל</v>
+      </c>
+      <c r="B38" t="str">
+        <v>2026-01-21</v>
+      </c>
+      <c r="C38" t="str">
+        <v>https://yosmusic.com/%d7%a7%d7%95%d7%91%d7%99-%d7%90%d7%a4%d7%9c%d7%9c%d7%95-%d7%99%d7%a9%d7%a8%d7%90%d7%9c/</v>
+      </c>
+      <c r="D38" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v>קובי אפללו שר "שראל”, פופ ים־תיכוני מלודי, נגיש  מנחם-מאחד.  אפללו בחר באסטרטגיה ברורה: האנשה של המדינה/העם בדמות אדם בשם “ישראל”, וכך להפוך סיפור לאומי־פוליטי לנרטיב רגשי־אישי. זו בחירה מוכרת בפופ הישראלי, אך כזו שעדיין עובדת כשהיא מבוצעת בכנות ובהתכוונות. הטקסט</v>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J38" t="str">
+        <v/>
+      </c>
+      <c r="K38" t="str">
+        <v/>
+      </c>
+      <c r="L38" t="str">
+        <v>קובי אפללו – ישראל</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>דניאל ג'מל – יוצאת מהקצב</v>
+      </c>
+      <c r="B39" t="str">
+        <v>2026-01-21</v>
+      </c>
+      <c r="C39" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%a0%d7%99%d7%90%d7%9c-%d7%92%d7%9e%d7%9c-%d7%99%d7%95%d7%a6%d7%90%d7%aa-%d7%9e%d7%94%d7%a7%d7%a6%d7%91/</v>
+      </c>
+      <c r="D39" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v>זהו שיר פופ קצבי, מלוטש ומיידי, שממוקם בבירור בתוך המיינסטרים של הפופ־המזרחי העכשווי. הוא עשוי היטב ברמה ההפקתית, אך סובל מתחושת דז׳ה־וו חזקה – הן מוזיקלית והן טקסטואלית. דניאל ג'מל (דה וויס 5) חוזר עם טקסט העוסק בפרידה לא סימטרית:</v>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J39" t="str">
+        <v/>
+      </c>
+      <c r="K39" t="str">
+        <v/>
+      </c>
+      <c r="L39" t="str">
+        <v>דניאל ג'מל – יוצאת מהקצב</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>מיקה קרני ואודי תורג'מן – כמו שהיה</v>
+      </c>
+      <c r="B40" t="str">
+        <v>2026-01-20</v>
+      </c>
+      <c r="C40" t="str">
+        <v>https://yosmusic.com/%d7%9e%d7%99%d7%a7%d7%94-%d7%a7%d7%a8%d7%a0%d7%99-%d7%95%d7%90%d7%95%d7%93%d7%99-%d7%aa%d7%95%d7%a8%d7%92%d7%9e%d7%9f-%d7%9b%d7%9e%d7%95-%d7%a9%d7%94%d7%99%d7%94/</v>
+      </c>
+      <c r="D40" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v>אודי תורג'מן ומיקה קרני פותחים את השיר בבית האחרון של הפואמה: “נתתי לך שעון במקוםטבעת נישואיןזמן עגול וטובשל נדודי שינה ונצח” הבית הזה הוא  תמצית של קשר שהומר מאידיליה רגשית לסמל מופשט של זמן, החמצה ונצח סדוק. כשהוא מוצב בפתיחה.</v>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+      <c r="I40" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J40" t="str">
+        <v/>
+      </c>
+      <c r="K40" t="str">
+        <v/>
+      </c>
+      <c r="L40" t="str">
+        <v>מיקה קרני ואודי תורג'מן – כמו שהיה</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>אביעד הנדל – טורקיז</v>
+      </c>
+      <c r="B41" t="str">
+        <v>2026-01-20</v>
+      </c>
+      <c r="C41" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%99%d7%a2%d7%93-%d7%94%d7%a0%d7%93%d7%9c-%d7%98%d7%95%d7%a8%d7%a7%d7%99%d7%96/</v>
+      </c>
+      <c r="D41" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v>אביעד הנדל מנסה להמחיש אווירה בשיר בקול רך מהורהר, לחן מינורי אפלולי בשיר סוריאליסטי.  הטקסט מתאר פכפוך, ציוץ ציפורים, צוקים וים – דימויים חזותיים ואוויריים. המוזיקה המינורית משקפת את ההרהור והספק של השאלות (“האם הדרך היא סלעית? האם כבושה?”). היא</v>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J41" t="str">
+        <v/>
+      </c>
+      <c r="K41" t="str">
+        <v/>
+      </c>
+      <c r="L41" t="str">
+        <v>אביעד הנדל – טורקיז</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Juno Vine – Space</v>
+      </c>
+      <c r="B42" t="str">
+        <v>2026-01-19</v>
+      </c>
+      <c r="C42" t="str">
+        <v>https://yosmusic.com/juno-vine-space/</v>
+      </c>
+      <c r="D42" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v>ג’ונו ויין (יונתן ויינרייך) שר בלדה רכה, אינטימית ומדויקת, שמצליחה לתאר תנועה בתוך קשר בלי דרמה מוחצנת, אלא דרך סדקים קטנים, מרחקים דקים וסאונד מחושב. כבר משם השיר ברור שלא מדובר בבריחה או ניתוק, אלא במצב תודעתי בתוך מערכת יחסים.</v>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J42" t="str">
+        <v/>
+      </c>
+      <c r="K42" t="str">
+        <v/>
+      </c>
+      <c r="L42" t="str">
+        <v>Juno Vine – Space</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>רונית שחר וקרני פוסטל – כישופים</v>
+      </c>
+      <c r="B43" t="str">
+        <v>2026-01-19</v>
+      </c>
+      <c r="C43" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a0%d7%99%d7%aa-%d7%a9%d7%97%d7%a8-%d7%95%d7%a7%d7%a8%d7%a0%d7%99-%d7%a4%d7%95%d7%a1%d7%98%d7%9c-%d7%9b%d7%99%d7%a9%d7%95%d7%a4%d7%99%d7%9d/</v>
+      </c>
+      <c r="D43" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v>שירה של דליה רביקוביץ, בלחן המקורי של מלכה שפיגל וקולין ניומן (1993), ובביצוע המחודש של רונית שחר וקרני פוסטל הוא קאבר שמעמיק את האינטימיות והעדינות של הטקסט דרך עיבוד מינימליסטי לגיטרות חשמליות וכלי מיתר אקוסטיים. שני קולות נשיים שרים טקסט</v>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J43" t="str">
+        <v/>
+      </c>
+      <c r="K43" t="str">
+        <v/>
+      </c>
+      <c r="L43" t="str">
+        <v>רונית שחר וקרני פוסטל – כישופים</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>פול טראנק – אין מילים איתך</v>
+      </c>
+      <c r="B44" t="str">
+        <v>2026-01-19</v>
+      </c>
+      <c r="C44" t="str">
+        <v>https://yosmusic.com/%d7%a4%d7%95%d7%9c-%d7%98%d7%a8%d7%90%d7%a0%d7%a7-%d7%90%d7%99%d7%9f-%d7%9e%d7%99%d7%9c%d7%99%d7%9d-%d7%90%d7%99%d7%aa%d7%9a/</v>
+      </c>
+      <c r="D44" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v>גל ניסמן שר בקול חשוף, נוגה וכואב בלדת אהבה. השיר נטוע עמוק בהווה – הפיד, מסכים, צילום מסך הלב כדי לשדר כמיהה. הדובר לא משתמש בדימויים הדיגיטליים כדי להקטין את הרגש, אלא כדי להודות שהוא חסר אמצעים מולו. המשפט החוזר</v>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J44" t="str">
+        <v/>
+      </c>
+      <c r="K44" t="str">
+        <v/>
+      </c>
+      <c r="L44" t="str">
+        <v>פול טראנק – אין מילים איתך</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>הילה רוח – טבע</v>
+      </c>
+      <c r="B45" t="str">
+        <v>2026-01-19</v>
+      </c>
+      <c r="C45" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%99%d7%9c%d7%94-%d7%a8%d7%95%d7%97-%d7%98%d7%91%d7%a2/</v>
+      </c>
+      <c r="D45" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v>זהו שיר מינורי, אפלולי ומודע לעצמו, שמצליח להיות אינטימי ופילוסופי בלי להתנשא. הילה רוח מציבה עימות בין הצורך האנושי בסגירה, סדר והיגיון לבין קשר שלא מציית לחוקים. ה”טבע” כאן אינו יער או נוף  אלא כוח בלתי נשלט: משיכה, כבידה, חזרתיות</v>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J45" t="str">
+        <v/>
+      </c>
+      <c r="K45" t="str">
+        <v/>
+      </c>
+      <c r="L45" t="str">
+        <v>הילה רוח – טבע</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>יובל רונן – מלאך‎</v>
+      </c>
+      <c r="B46" t="str">
+        <v>2026-01-17</v>
+      </c>
+      <c r="C46" t="str">
+        <v>https://yosmusic.com/%d7%99%d7%95%d7%91%d7%9c-%d7%a8%d7%95%d7%a0%d7%9f-%d7%9e%d7%9c%d7%90%d7%9a/</v>
+      </c>
+      <c r="D46" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v>"מלאך” של יובל רונן הוא שיר התבגרות רגשית במסווה של סיפור אגדי. זהו שיר על אהבה חדשה שמופיעה ברגע של שבר פנימי, ומציעה לא גאולה מלאה – אלא הפוגה. המעבר המוזיקלי משירה כמעט מלוחשת לקצב ואלס אינו רק אמצעי מוזיקלי,</v>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J46" t="str">
+        <v/>
+      </c>
+      <c r="K46" t="str">
+        <v/>
+      </c>
+      <c r="L46" t="str">
+        <v>יובל רונן – מלאך‎</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>צחי אלוש – מפלצת</v>
+      </c>
+      <c r="B47" t="str">
+        <v>2026-01-16</v>
+      </c>
+      <c r="C47" t="str">
+        <v>https://yosmusic.com/%d7%a6%d7%97%d7%99-%d7%90%d7%9c%d7%95%d7%a9-%d7%9e%d7%a4%d7%9c%d7%a6%d7%aa/</v>
+      </c>
+      <c r="D47" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v>„מפלצת” היא בלדת רוק מלנכולית פנימית איטית, שמתמקדת לא באיום חיצוני אלא בזהות מתפוררת מבפנים. זהו שיר וידוי, כמעט יומן נפשי, שבו הגיטרה החשמלית לא “מובילה” את השיר – אלא נושמת יחד עם הטקסט. המפלצת שבצחי אלוש אינה דימוי פנטסטי,</v>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
+      <c r="I47" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J47" t="str">
+        <v/>
+      </c>
+      <c r="K47" t="str">
+        <v/>
+      </c>
+      <c r="L47" t="str">
+        <v>צחי אלוש – מפלצת</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>שניר עזרן – אין מה לדאוג</v>
+      </c>
+      <c r="B48" t="str">
+        <v>2026-01-15</v>
+      </c>
+      <c r="C48" t="str">
+        <v>https://yosmusic.com/%d7%a9%d7%a0%d7%99%d7%a8-%d7%a2%d7%96%d7%a8%d7%9f-%d7%90%d7%99%d7%9f-%d7%9e%d7%94-%d7%9c%d7%93%d7%90%d7%95%d7%92/</v>
+      </c>
+      <c r="D48" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v>השיר נטוע עמוק בז’אנר פופ ים־תיכוני מיד־טמפו מרומם נפש, כזה שמאפיין תקופות של חיפוש פנימי וקבלת החלטות. זהו שיר של מעבר: בין ספק לאמונה, בין פחד לרוגע, בין פעולה להשלמה. הקצב הבינוני מאפשר לשיר להיות גם מדיטטיבי וגם נגיש לרדיו,</v>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
+      <c r="I48" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J48" t="str">
+        <v/>
+      </c>
+      <c r="K48" t="str">
+        <v/>
+      </c>
+      <c r="L48" t="str">
+        <v>שניר עזרן – אין מה לדאוג</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>שולי רנד – לב לבן</v>
+      </c>
+      <c r="B49" t="str">
+        <v>2026-01-14</v>
+      </c>
+      <c r="C49" t="str">
+        <v>https://yosmusic.com/%d7%a9%d7%95%d7%9c%d7%99-%d7%a8%d7%a0%d7%93-%d7%9c%d7%91-%d7%9c%d7%91%d7%9f/</v>
+      </c>
+      <c r="D49" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v>"לב לבן” של שולי רנד הוא שיר אהבה שיש בו רוך, אבל גם הכרעה. אהבה כאן היא לא מפלט מהעולם, אלא דרך להיות בו אחרת. זהו שיר קבלה לא של רגע שיא רומנטי, אלא של הגעה אחרי דרך ארוכה, יבשה,</v>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+      <c r="H49" t="str">
+        <v/>
+      </c>
+      <c r="I49" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J49" t="str">
+        <v/>
+      </c>
+      <c r="K49" t="str">
+        <v/>
+      </c>
+      <c r="L49" t="str">
+        <v>שולי רנד – לב לבן</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>דודי בר דוד – הארץ המובטחת</v>
+      </c>
+      <c r="B50" t="str">
+        <v>2026-01-14</v>
+      </c>
+      <c r="C50" t="str">
+        <v>https://yosmusic.com/%d7%93%d7%95%d7%93%d7%99-%d7%91%d7%a8-%d7%93%d7%95%d7%93-%d7%94%d7%90%d7%a8%d7%a5-%d7%94%d7%9e%d7%95%d7%91%d7%98%d7%97%d7%aa/</v>
+      </c>
+      <c r="D50" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v>"הארץ המובטחת” של דודי בר-דוד משתמש בקצב נסיעה כאלגוריה לחיפוש זהות ישראלית־אישית: בן מול אב, עבר מול עתיד, אמונה מול ריק. זה שיר של נוסע קדימה, אבל כל הזמן מסתכל במראה. כבר מהשורה הראשונה ברור שזה שיר דרך – אבל</v>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
+      <c r="I50" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J50" t="str">
+        <v/>
+      </c>
+      <c r="K50" t="str">
+        <v/>
+      </c>
+      <c r="L50" t="str">
+        <v>דודי בר דוד – הארץ המובטחת</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>שלום גד וערן צור – תחזור לנגן בס</v>
+      </c>
+      <c r="B51" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C51" t="str">
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%95%d7%9d-%d7%92%d7%93-%d7%95%d7%a2%d7%a8%d7%9f-%d7%a6%d7%95%d7%a8-%d7%aa%d7%97%d7%96%d7%95%d7%a8-%d7%9c%d7%a0%d7%92%d7%9f-%d7%91%d7%a1/</v>
+      </c>
+      <c r="D51" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v>זה שיר חזק, מטא-מוזיקלי, וכואב, ובעיקר כזה שמדבר מתוך הסצנה הישראלית אל עצמה. ״תחזור לנגן בס״ הוא הרבה יותר מהוראה טכנית: זה שיר על זהות, אובדן דרך, ועל הצלה דרך מוזיקה. זה שיר דרמטי־וידויי של שלום גד, שבו ערן צור</v>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+      <c r="H51" t="str">
+        <v/>
+      </c>
+      <c r="I51" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J51" t="str">
+        <v/>
+      </c>
+      <c r="K51" t="str">
+        <v/>
+      </c>
+      <c r="L51" t="str">
+        <v>שלום גד וערן צור – תחזור לנגן בס</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>האחיות – בואו איתי</v>
+      </c>
+      <c r="B52" t="str">
+        <v>2026-01-13</v>
+      </c>
+      <c r="C52" t="str">
+        <v>https://yosmusic.com/%d7%94%d7%90%d7%97%d7%99%d7%95%d7%aa-%d7%91%d7%95%d7%90%d7%95-%d7%90%d7%99%d7%aa%d7%99/</v>
+      </c>
+      <c r="D52" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <v>הפשטות היא הכוח. זה שיר שנשמע כמו משהו שתמיד היה כאן, גם אם הוא חדש. "האחיות" – זוהר גינזבורג, טולה בן ארי, מיקה שדה שרות שיר פולק בסגנון אולד סקול , לא וידוי אישי, לא סיפור פרטי, אלא קריאה. הזמנה</v>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+      <c r="H52" t="str">
+        <v/>
+      </c>
+      <c r="I52" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J52" t="str">
+        <v/>
+      </c>
+      <c r="K52" t="str">
+        <v/>
+      </c>
+      <c r="L52" t="str">
+        <v>האחיות – בואו איתי</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>עידו מלכה – כמה שלא ניסיתי</v>
+      </c>
+      <c r="B53" t="str">
+        <v>2026-01-12</v>
+      </c>
+      <c r="C53" t="str">
+        <v>https://yosmusic.com/%d7%a2%d7%99%d7%93%d7%95-%d7%9e%d7%9c%d7%9b%d7%94-%d7%9b%d7%9e%d7%94-%d7%a9%d7%9c%d7%90-%d7%a0%d7%99%d7%a1%d7%99%d7%aa%d7%99/</v>
+      </c>
+      <c r="D53" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+      <c r="F53" t="str">
+        <v>"כמה שלא ניסיתי” הוא שיר פופ רומנטי טהור על אהבה ראשונה שלא קורית. לא דרמה גדולה, לא שברון לב טראגי  אלא אכזבה מתוקה־מרירה, כזו שכולנו מכירים מהגיל שבו הרגש גדול מהכלים שיש לנו להתמודד איתו. כבר בבית הראשון אנחנו בתוך</v>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
+      <c r="I53" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J53" t="str">
+        <v/>
+      </c>
+      <c r="K53" t="str">
+        <v/>
+      </c>
+      <c r="L53" t="str">
+        <v>עידו מלכה – כמה שלא ניסיתי</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>אסף אמדורסקי – עד שירדו דמעות</v>
+      </c>
+      <c r="B54" t="str">
+        <v>2026-01-12</v>
+      </c>
+      <c r="C54" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%a1%d7%a3-%d7%90%d7%9e%d7%93%d7%95%d7%a8%d7%a1%d7%a7%d7%99-%d7%a2%d7%93-%d7%a9%d7%99%d7%a8%d7%93%d7%95-%d7%93%d7%9e%d7%a2%d7%95%d7%aa/</v>
+      </c>
+      <c r="D54" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v>זה לגמרי אמדורסקי במוד שלו – אינטימי, חושני, קצת מנוכר וקצת פגיע. ״עד שירדו דמעות״ מצטייר כשיר תשוקה לילי, כמעט קולנועי, שמתרחש במרחב שבין גוף לנפש. אין כאן סיפור ליניארי, אלא רצף של רגעים, מגעים והבהובים רגשיים. הכול קורה עכשיו,</v>
+      </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
+      <c r="H54" t="str">
+        <v/>
+      </c>
+      <c r="I54" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J54" t="str">
+        <v/>
+      </c>
+      <c r="K54" t="str">
+        <v/>
+      </c>
+      <c r="L54" t="str">
+        <v>אסף אמדורסקי – עד שירדו דמעות</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>ליר – אני רוצה לשיר</v>
+      </c>
+      <c r="B55" t="str">
+        <v>2026-01-11</v>
+      </c>
+      <c r="C55" t="str">
+        <v>https://yosmusic.com/%d7%9c%d7%99%d7%a8-%d7%90%d7%a0%d7%99-%d7%a8%d7%95%d7%a6%d7%94-%d7%9c%d7%a9%d7%99%d7%a8/</v>
+      </c>
+      <c r="D55" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <v>המשפט “אני רוצה לשיר” ששרה ליר חוטובלי  לא מדבר על שירה כמטרה בלבדית  שעומדת בפני עצמה. השירה כאן היא דרך לפרוק, דרך להתקרב, דרך להמשיך למרות הכאב, דרך לאהוב. השירה – אמצעי לא מטרה. המלודיה שלה בנויה סימטרית וברורה –</v>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+      <c r="H55" t="str">
+        <v/>
+      </c>
+      <c r="I55" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J55" t="str">
+        <v/>
+      </c>
+      <c r="K55" t="str">
+        <v/>
+      </c>
+      <c r="L55" t="str">
+        <v>ליר – אני רוצה לשיר</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>אברהם טל וטוהר גדסי – הכל יעבור</v>
+      </c>
+      <c r="B56" t="str">
+        <v>2026-01-11</v>
+      </c>
+      <c r="C56" t="str">
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%95%d7%98%d7%95%d7%94%d7%a8-%d7%92%d7%93%d7%a1%d7%99-%d7%94%d7%9b%d7%9c-%d7%99%d7%a2%d7%91%d7%95%d7%a8/</v>
+      </c>
+      <c r="D56" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v>,הכל יעבור” בדואט אברהם טל וטוהר גדסי הוא שיר שנולד במודע מתוך רגע חברתי־רגשי: שיחת סלון, עייפות מהקיטוב, רצון להרגיע. זה לא שיר שנכתב כפואטיקה צרופה, אלא מתוך מצב. השניים מכוונים לשיר מחבק, אופטימי, מפייס, שיר שמניח פלסטר רגשי על</v>
+      </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
+      <c r="H56" t="str">
+        <v/>
+      </c>
+      <c r="I56" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J56" t="str">
+        <v/>
+      </c>
+      <c r="K56" t="str">
+        <v/>
+      </c>
+      <c r="L56" t="str">
+        <v>אברהם טל וטוהר גדסי – הכל יעבור</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>בן שוקרון – אמצע העולם</v>
+      </c>
+      <c r="B57" t="str">
+        <v>2026-01-10</v>
+      </c>
+      <c r="C57" t="str">
+        <v>https://yosmusic.com/%d7%91%d7%9f-%d7%a9%d7%95%d7%a7%d7%a8%d7%95%d7%9f-%d7%90%d7%9e%d7%a6%d7%a2-%d7%94%d7%a2%d7%95%d7%9c%d7%9d/</v>
+      </c>
+      <c r="D57" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v>“אמצע העולם” של בן שוקרון הוא בלדת־דרך ישראלית, כזו שנעה על קצב מידטמפו יציב, כמו נסיעה ארוכה בכביש מוכר- לא ממהרת, לא בורחת, פשוט ממשיכה. הפתיחה – “שביל קטן באמצע העולם” היא הצהרה זהותית חזקה: המקום קטן, אולי שולי על</v>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+      <c r="H57" t="str">
+        <v/>
+      </c>
+      <c r="I57" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J57" t="str">
+        <v/>
+      </c>
+      <c r="K57" t="str">
+        <v/>
+      </c>
+      <c r="L57" t="str">
+        <v>בן שוקרון – אמצע העולם</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>סטלה – בלרינה</v>
+      </c>
+      <c r="B58" t="str">
+        <v>2026-01-08</v>
+      </c>
+      <c r="C58" t="str">
+        <v>https://yosmusic.com/%d7%a1%d7%98%d7%9c%d7%94-%d7%91%d7%9c%d7%a8%d7%99%d7%a0%d7%94/</v>
+      </c>
+      <c r="D58" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v>דרך אנרגיה רוקית, שפה חצופה ומודעות עצמית חדה, סטלה מושאילוב שרה שיר אישי מאוד וגם מספיק חד כדי שמי ששומעת אותה ירגיש שהוא נכתב עליה. הבלרינה כאן היא הציפייה להיות עדינה, ממושמעת, יפה במובן המאולף, וכשהיא אומרת: – “אני אף</v>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+      <c r="H58" t="str">
+        <v/>
+      </c>
+      <c r="I58" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J58" t="str">
+        <v/>
+      </c>
+      <c r="K58" t="str">
+        <v/>
+      </c>
+      <c r="L58" t="str">
+        <v>סטלה – בלרינה</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>יערה לוי – מתי זה יפסק</v>
+      </c>
+      <c r="B59" t="str">
+        <v>2026-01-07</v>
+      </c>
+      <c r="C59" t="str">
+        <v>https://yosmusic.com/%d7%99%d7%a2%d7%a8%d7%94-%d7%9c%d7%95%d7%99-%d7%9e%d7%aa%d7%99-%d7%96%d7%94-%d7%99%d7%a4%d7%a1%d7%a7/</v>
+      </c>
+      <c r="D59" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v>יערה לוי שרה שרה את שברון ליבה על מערכת יחסים מורכבת בין בני זוג, מנקודת מבטה של מישהי שעייפה רגשית. על משיכה לצד תסכול, על ניסיונות שלא נגמרים, על חיפוש אחרי משהו אמיתי- ועל הרגע שבו כבר אין כוח להתחיל</v>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+      <c r="H59" t="str">
+        <v/>
+      </c>
+      <c r="I59" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J59" t="str">
+        <v/>
+      </c>
+      <c r="K59" t="str">
+        <v/>
+      </c>
+      <c r="L59" t="str">
+        <v>יערה לוי – מתי זה יפסק</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>נינט טייב – אולי יכולתי יותר</v>
+      </c>
+      <c r="B60" t="str">
+        <v>2026-01-07</v>
+      </c>
+      <c r="C60" t="str">
+        <v>https://yosmusic.com/%d7%a0%d7%99%d7%a0%d7%98-%d7%98%d7%99%d7%99%d7%91-%d7%90%d7%95%d7%9c%d7%99-%d7%99%d7%9b%d7%95%d7%9c%d7%aa%d7%99-%d7%99%d7%95%d7%aa%d7%a8/</v>
+      </c>
+      <c r="D60" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v>זה שיר שמבקש לא לצעוק כאב – אלא להודות בו בכאב "לא ידעתי שככה הכאב מדבר/ אולי יכולתי יותר/ אולי יכולתי יותר/ אולי יכולתי יותר". נינט שרה באזור גבוה יחסית, אבל בלי כוחנות, בלי “שואו”, עם תחושת ריחוף שברירי. זה</v>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+      <c r="H60" t="str">
+        <v/>
+      </c>
+      <c r="I60" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J60" t="str">
+        <v/>
+      </c>
+      <c r="K60" t="str">
+        <v/>
+      </c>
+      <c r="L60" t="str">
+        <v>נינט טייב – אולי יכולתי יותר</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>שיר לוי – רחוב ללא מוצא</v>
+      </c>
+      <c r="B61" t="str">
+        <v>2026-01-07</v>
+      </c>
+      <c r="C61" t="str">
+        <v>https://yosmusic.com/%d7%a9%d7%99%d7%a8-%d7%9c%d7%95%d7%99-%d7%a8%d7%97%d7%95%d7%91-%d7%9c%d7%9c%d7%90-%d7%9e%d7%95%d7%a6%d7%90/</v>
+      </c>
+      <c r="D61" t="str">
+        <v>2026-01-24</v>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v>שיר לוי שר בלדה שמתחילה מהאדמה, עוברת דרך שבר, ומרימה את הראש אל איזו נקודת אור.המסע בשיר אינו ליניארי. אין “עברתי את זה”. להפך: "שוב נכשל ושוב נופל/ אז אני קם ומתפלל” זהו מסע של מצבים חוזרים: נפילה, תפילה, אחיזה</v>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+      <c r="H61" t="str">
+        <v/>
+      </c>
+      <c r="I61" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J61" t="str">
+        <v/>
+      </c>
+      <c r="K61" t="str">
+        <v/>
+      </c>
+      <c r="L61" t="str">
+        <v>שיר לוי – רחוב ללא מוצא</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L61"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-01-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-01-week04/titles.xlsx
@@ -442,7 +442,7 @@
         <v>2026-01-24</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409306&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409306&amp;sid=55bb241e9c2691569a101a094b96c0a8</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-24</v>
@@ -480,7 +480,7 @@
         <v>2026-01-24</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409328&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409328&amp;sid=55bb241e9c2691569a101a094b96c0a8</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-24</v>
@@ -518,7 +518,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409327&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409327&amp;sid=55bb241e9c2691569a101a094b96c0a8</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-24</v>
@@ -556,7 +556,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409326&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409326&amp;sid=55bb241e9c2691569a101a094b96c0a8</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-24</v>
@@ -594,7 +594,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409325&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409325&amp;sid=55bb241e9c2691569a101a094b96c0a8</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-24</v>
@@ -632,7 +632,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409324&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409324&amp;sid=55bb241e9c2691569a101a094b96c0a8</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-24</v>
@@ -670,7 +670,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409323&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409323&amp;sid=55bb241e9c2691569a101a094b96c0a8</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-24</v>
@@ -708,7 +708,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409322&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409322&amp;sid=55bb241e9c2691569a101a094b96c0a8</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-24</v>
@@ -746,7 +746,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409321&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409321&amp;sid=55bb241e9c2691569a101a094b96c0a8</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-24</v>
@@ -784,7 +784,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409320&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409320&amp;sid=55bb241e9c2691569a101a094b96c0a8</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-24</v>
@@ -822,7 +822,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409319&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409319&amp;sid=55bb241e9c2691569a101a094b96c0a8</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-24</v>
@@ -860,7 +860,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409318&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409318&amp;sid=55bb241e9c2691569a101a094b96c0a8</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-24</v>
@@ -898,7 +898,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409317&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409317&amp;sid=55bb241e9c2691569a101a094b96c0a8</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-24</v>
@@ -936,7 +936,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409316&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409316&amp;sid=55bb241e9c2691569a101a094b96c0a8</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-24</v>
@@ -974,7 +974,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409315&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409315&amp;sid=55bb241e9c2691569a101a094b96c0a8</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-24</v>
@@ -1012,7 +1012,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409314&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409314&amp;sid=55bb241e9c2691569a101a094b96c0a8</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-24</v>
@@ -1050,7 +1050,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409313&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409313&amp;sid=55bb241e9c2691569a101a094b96c0a8</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-24</v>
@@ -1088,7 +1088,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409312&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409312&amp;sid=55bb241e9c2691569a101a094b96c0a8</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-24</v>
@@ -1126,7 +1126,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409311&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409311&amp;sid=55bb241e9c2691569a101a094b96c0a8</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-24</v>
@@ -1164,7 +1164,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409310&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409310&amp;sid=55bb241e9c2691569a101a094b96c0a8</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-24</v>
@@ -1202,7 +1202,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409309&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409309&amp;sid=55bb241e9c2691569a101a094b96c0a8</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-24</v>
@@ -1240,7 +1240,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C23" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409308&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409308&amp;sid=55bb241e9c2691569a101a094b96c0a8</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-24</v>
@@ -1278,7 +1278,7 @@
         <v>2026-01-21</v>
       </c>
       <c r="C24" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409307&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409307&amp;sid=55bb241e9c2691569a101a094b96c0a8</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-24</v>
@@ -1316,7 +1316,7 @@
         <v>2026-01-21</v>
       </c>
       <c r="C25" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409305&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409305&amp;sid=55bb241e9c2691569a101a094b96c0a8</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-24</v>
@@ -1354,7 +1354,7 @@
         <v>2026-01-21</v>
       </c>
       <c r="C26" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409304&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409304&amp;sid=55bb241e9c2691569a101a094b96c0a8</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-24</v>
@@ -1392,7 +1392,7 @@
         <v>2026-01-21</v>
       </c>
       <c r="C27" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409303&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409303&amp;sid=55bb241e9c2691569a101a094b96c0a8</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-24</v>
@@ -1430,7 +1430,7 @@
         <v>2026-01-21</v>
       </c>
       <c r="C28" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409302&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409302&amp;sid=55bb241e9c2691569a101a094b96c0a8</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-24</v>
@@ -1468,7 +1468,7 @@
         <v>2026-01-21</v>
       </c>
       <c r="C29" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409301&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409301&amp;sid=55bb241e9c2691569a101a094b96c0a8</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-24</v>
@@ -1506,7 +1506,7 @@
         <v>2026-01-21</v>
       </c>
       <c r="C30" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409300&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409300&amp;sid=55bb241e9c2691569a101a094b96c0a8</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-24</v>
@@ -1544,7 +1544,7 @@
         <v>2026-01-21</v>
       </c>
       <c r="C31" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409299&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409299&amp;sid=55bb241e9c2691569a101a094b96c0a8</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-24</v>

--- a/data/tags/סינגלים חדשים/global/2026-01-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-01-week04/titles.xlsx
@@ -436,7 +436,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אביב גפן וברי סחרוף מנגינת הלב</v>
+        <v>אביב גפן וברי סחרוף – מנגינת הלב</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-25</v>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אביב גפן וברי סחרוף מנגינת הלב</v>
+        <v>אביב גפן וברי סחרוף – מנגינת הלב</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-01-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-01-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אביב גפן וברי סחרוף – מנגינת הלב</v>
+        <v>יהורם גאון וסאבלימינל – לא אהבתי די</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-25</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%91%d7%99%d7%91-%d7%92%d7%a4%d7%9f-%d7%95%d7%91%d7%a8%d7%99-%d7%a1%d7%97%d7%a8%d7%95%d7%a3-%d7%9e%d7%a0%d7%92%d7%99%d7%a0%d7%aa-%d7%94%d7%9c%d7%91/</v>
+        <v>https://yosmusic.com/%d7%99%d7%94%d7%95%d7%a8%d7%9d-%d7%92%d7%90%d7%95%d7%9f-%d7%95%d7%a1%d7%90%d7%91%d7%9c%d7%99%d7%9e%d7%99%d7%a0%d7%9c-%d7%9c%d7%90-%d7%90%d7%94%d7%91%d7%aa%d7%99-%d7%93%d7%99/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-25</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הדואט נוגע בלב הדילמה סביב אביב גפן בעשור האחרון – וגם סביב עצם הרעיון של “שיר אופטימי” במציאות ישראלית פצועה.  השיר מצייר מציאות שאחרי טראומה, לא מציאות “מושלמת”: – “יש איזה רוח שנושבת גם אם אתה עומד במקום”. זו לא</v>
+        <v>מדובר לא רק בביצוע מחודש אלא בשכתוב תרבותי: מפגש בין נעמי שמר, יהורם גאון, וסאבלימינל – עולמות שלא נועדו זה לזה מכל בחינה. מצד שני: זה שיר שמייצר גשר בין דור החלוצים לדור דור ההיפ-הופ, בין קולקטיב  לאינדיבידואל המקור של</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אביב גפן וברי סחרוף – מנגינת הלב</v>
+        <v>יהורם גאון וסאבלימינל – לא אהבתי די</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-01-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יהורם גאון וסאבלימינל – לא אהבתי די</v>
+        <v>אבי בן ישראל - ברכה עליהם</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-25</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%94%d7%95%d7%a8%d7%9d-%d7%92%d7%90%d7%95%d7%9f-%d7%95%d7%a1%d7%90%d7%91%d7%9c%d7%99%d7%9e%d7%99%d7%a0%d7%9c-%d7%9c%d7%90-%d7%90%d7%94%d7%91%d7%aa%d7%99-%d7%93%d7%99/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409347&amp;sid=4911af2243704a7b759f3f06503a8845</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-25</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>מדובר לא רק בביצוע מחודש אלא בשכתוב תרבותי: מפגש בין נעמי שמר, יהורם גאון, וסאבלימינל – עולמות שלא נועדו זה לזה מכל בחינה. מצד שני: זה שיר שמייצר גשר בין דור החלוצים לדור דור ההיפ-הופ, בין קולקטיב  לאינדיבידואל המקור של</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,50 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יהורם גאון וסאבלימינל – לא אהבתי די</v>
+        <v>אבי בן ישראל - ברכה עליהם</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>LioZee - הלב שלי אלייך</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-01-25</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409346&amp;sid=4911af2243704a7b759f3f06503a8845</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-01-25</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>LioZee - הלב שלי אלייך</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-01-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אבי בן ישראל - ברכה עליהם</v>
+        <v>איתי בירמן - אין אהבה ללא כאב</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-25</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409347&amp;sid=4911af2243704a7b759f3f06503a8845</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409354&amp;sid=db9290d6a92d2aea07f4f78064fb5bbd</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-25</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אבי בן ישראל - ברכה עליהם</v>
+        <v>איתי בירמן - אין אהבה ללא כאב</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>LioZee - הלב שלי אלייך</v>
+        <v>אור סלמן - מכתוב</v>
       </c>
       <c r="B3" t="str">
         <v>2026-01-25</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409346&amp;sid=4911af2243704a7b759f3f06503a8845</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409353&amp;sid=db9290d6a92d2aea07f4f78064fb5bbd</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-25</v>
@@ -507,12 +507,202 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>LioZee - הלב שלי אלייך</v>
+        <v>אור סלמן - מכתוב</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>אברהם איילאו &amp; אופק אדנק - מעגל</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-01-25</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409352&amp;sid=db9290d6a92d2aea07f4f78064fb5bbd</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-01-25</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>אברהם איילאו &amp; אופק אדנק - מעגל</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>אבישי עוזיאל - מיטה ספוגה בדמעות</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-01-25</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409351&amp;sid=db9290d6a92d2aea07f4f78064fb5bbd</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-01-25</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>אבישי עוזיאל - מיטה ספוגה בדמעות</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>אבירם פרחן - נשמה</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-01-25</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409350&amp;sid=db9290d6a92d2aea07f4f78064fb5bbd</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-01-25</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>אבירם פרחן - נשמה</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>אביב גפן &amp; ברי סחרוף - מנגינת הלב</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-01-25</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409349&amp;sid=db9290d6a92d2aea07f4f78064fb5bbd</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-01-25</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>אביב גפן &amp; ברי סחרוף - מנגינת הלב</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אבי לרנר - ותהי שמחה</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-01-25</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409348&amp;sid=db9290d6a92d2aea07f4f78064fb5bbd</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-01-25</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אבי לרנר - ותהי שמחה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-01-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>איתי בירמן - אין אהבה ללא כאב</v>
+        <v>שחר טבוך - טוק טו מי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-25</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409354&amp;sid=db9290d6a92d2aea07f4f78064fb5bbd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409360&amp;sid=b7a7b3545106de0938a1dbb945510b0d</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-25</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>איתי בירמן - אין אהבה ללא כאב</v>
+        <v>שחר טבוך - טוק טו מי</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אור סלמן - מכתוב</v>
+        <v>נפתלי חיים - מחרוזת חופה 2026</v>
       </c>
       <c r="B3" t="str">
         <v>2026-01-25</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409353&amp;sid=db9290d6a92d2aea07f4f78064fb5bbd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409359&amp;sid=b7a7b3545106de0938a1dbb945510b0d</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-25</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אור סלמן - מכתוב</v>
+        <v>נפתלי חיים - מחרוזת חופה 2026</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אברהם איילאו &amp; אופק אדנק - מעגל</v>
+        <v>יקיר יהודה יאיר - הולך איתי</v>
       </c>
       <c r="B4" t="str">
         <v>2026-01-25</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409352&amp;sid=db9290d6a92d2aea07f4f78064fb5bbd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409358&amp;sid=b7a7b3545106de0938a1dbb945510b0d</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-25</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>אברהם איילאו &amp; אופק אדנק - מעגל</v>
+        <v>יקיר יהודה יאיר - הולך איתי</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>אבישי עוזיאל - מיטה ספוגה בדמעות</v>
+        <v>יהונתן דרזי - לב שבור</v>
       </c>
       <c r="B5" t="str">
         <v>2026-01-25</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409351&amp;sid=db9290d6a92d2aea07f4f78064fb5bbd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409357&amp;sid=b7a7b3545106de0938a1dbb945510b0d</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-25</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>אבישי עוזיאל - מיטה ספוגה בדמעות</v>
+        <v>יהונתן דרזי - לב שבור</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>אבירם פרחן - נשמה</v>
+        <v>יהודה בורן &amp; נתנאל אמסילי - אילן קאבר</v>
       </c>
       <c r="B6" t="str">
         <v>2026-01-25</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409350&amp;sid=db9290d6a92d2aea07f4f78064fb5bbd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409356&amp;sid=b7a7b3545106de0938a1dbb945510b0d</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-25</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>אבירם פרחן - נשמה</v>
+        <v>יהודה בורן &amp; נתנאל אמסילי - אילן קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>אביב גפן &amp; ברי סחרוף - מנגינת הלב</v>
+        <v>בן אגם - ראש בראש</v>
       </c>
       <c r="B7" t="str">
         <v>2026-01-25</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409349&amp;sid=db9290d6a92d2aea07f4f78064fb5bbd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409355&amp;sid=b7a7b3545106de0938a1dbb945510b0d</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-25</v>
@@ -659,50 +659,12 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>אביב גפן &amp; ברי סחרוף - מנגינת הלב</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>אבי לרנר - ותהי שמחה</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-01-25</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409348&amp;sid=db9290d6a92d2aea07f4f78064fb5bbd</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-01-25</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>אבי לרנר - ותהי שמחה</v>
+        <v>בן אגם - ראש בראש</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-01-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שחר טבוך - טוק טו מי</v>
+        <v>יגל יובל שרעבי - סור מרע ועשה טוב</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-25</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409360&amp;sid=b7a7b3545106de0938a1dbb945510b0d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409361&amp;sid=bb2b773653d416cfdab81cc6be2fe852</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-25</v>
@@ -469,202 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שחר טבוך - טוק טו מי</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>נפתלי חיים - מחרוזת חופה 2026</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-01-25</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409359&amp;sid=b7a7b3545106de0938a1dbb945510b0d</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-01-25</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>נפתלי חיים - מחרוזת חופה 2026</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>יקיר יהודה יאיר - הולך איתי</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-01-25</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409358&amp;sid=b7a7b3545106de0938a1dbb945510b0d</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-01-25</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>יקיר יהודה יאיר - הולך איתי</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>יהונתן דרזי - לב שבור</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-01-25</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409357&amp;sid=b7a7b3545106de0938a1dbb945510b0d</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-01-25</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>יהונתן דרזי - לב שבור</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>יהודה בורן &amp; נתנאל אמסילי - אילן קאבר</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-01-25</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409356&amp;sid=b7a7b3545106de0938a1dbb945510b0d</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-01-25</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>יהודה בורן &amp; נתנאל אמסילי - אילן קאבר</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>בן אגם - ראש בראש</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-01-25</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409355&amp;sid=b7a7b3545106de0938a1dbb945510b0d</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-01-25</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>בן אגם - ראש בראש</v>
+        <v>יגל יובל שרעבי - סור מרע ועשה טוב</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-01-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-01-week04/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יגל יובל שרעבי - סור מרע ועשה טוב</v>
+        <v>עדן בן זקן – רולקס וקסקט</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409361&amp;sid=bb2b773653d416cfdab81cc6be2fe852</v>
+        <v>https://yosmusic.com/%d7%a2%d7%93%d7%9f-%d7%91%d7%9f-%d7%96%d7%a7%d7%9f-%d7%a8%d7%95%d7%9c%d7%a7%d7%a1-%d7%95%d7%a7%d7%a1%d7%a7%d7%98/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>השיר ששרה עדן בן זקן יושב  על קו התפר בין בלדת פופ, ים־תיכוני מודרני לפופ – והוא מדגים היטב את מצב הז’אנר היום: תעשייתי, אפקטיבי, ולעיתים קרובות צפוי, גם את העובדה שבן זקן ממשיכה להישען כל יצרני שירים שמתאימים לז'אנר</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יגל יובל שרעבי - סור מרע ועשה טוב</v>
+        <v>עדן בן זקן – רולקס וקסקט</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-01-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-01-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עדן בן זקן – רולקס וקסקט</v>
+        <v>הפטריקים – תשאירי לי מקום לחבק אותך</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-26</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a2%d7%93%d7%9f-%d7%91%d7%9f-%d7%96%d7%a7%d7%9f-%d7%a8%d7%95%d7%9c%d7%a7%d7%a1-%d7%95%d7%a7%d7%a1%d7%a7%d7%98/</v>
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%98%d7%a8%d7%99%d7%a7%d7%99%d7%9d-%d7%aa%d7%a9%d7%90%d7%99%d7%a8%d7%99-%d7%9c%d7%99-%d7%9e%d7%a7%d7%95%d7%9d-%d7%9c%d7%97%d7%91%d7%a7-%d7%90%d7%95%d7%aa%d7%9a/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-26</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר ששרה עדן בן זקן יושב  על קו התפר בין בלדת פופ, ים־תיכוני מודרני לפופ – והוא מדגים היטב את מצב הז’אנר היום: תעשייתי, אפקטיבי, ולעיתים קרובות צפוי, גם את העובדה שבן זקן ממשיכה להישען כל יצרני שירים שמתאימים לז'אנר</v>
+        <v>הפטריקים – הפרויקט של דודי לוי ואבטיפוס – עושים צעד קידום מכירות מסחרי מובהק: הם מוציאים אלבום של "להיטי זהב" מכל הרפרטואר של חברי הלהקה ("אבטיפוס", "נוער שוליים"). "תשאירי לי מקום לחבק אותך" הוא הקאבר הראשון שנבחר כסינגל. כתבתי בעבר</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עדן בן זקן – רולקס וקסקט</v>
+        <v>הפטריקים – תשאירי לי מקום לחבק אותך</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-01-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>הפטריקים – תשאירי לי מקום לחבק אותך</v>
+        <v>שימי לנגא - שיר תודה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-26</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%a4%d7%98%d7%a8%d7%99%d7%a7%d7%99%d7%9d-%d7%aa%d7%a9%d7%90%d7%99%d7%a8%d7%99-%d7%9c%d7%99-%d7%9e%d7%a7%d7%95%d7%9d-%d7%9c%d7%97%d7%91%d7%a7-%d7%90%d7%95%d7%aa%d7%9a/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409370&amp;sid=eae9911b6505b4b3636087b09a75bd12</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-26</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הפטריקים – הפרויקט של דודי לוי ואבטיפוס – עושים צעד קידום מכירות מסחרי מובהק: הם מוציאים אלבום של "להיטי זהב" מכל הרפרטואר של חברי הלהקה ("אבטיפוס", "נוער שוליים"). "תשאירי לי מקום לחבק אותך" הוא הקאבר הראשון שנבחר כסינגל. כתבתי בעבר</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,316 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>הפטריקים – תשאירי לי מקום לחבק אותך</v>
+        <v>שימי לנגא - שיר תודה</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>רגב הוד - לירז</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-01-26</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409369&amp;sid=eae9911b6505b4b3636087b09a75bd12</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-01-26</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>רגב הוד - לירז</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>פן חזות - בואי</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-01-26</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409368&amp;sid=eae9911b6505b4b3636087b09a75bd12</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-01-26</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>פן חזות - בואי</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>עופר לוי &amp; הגר יפת - חיים של אמא</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-01-26</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409367&amp;sid=eae9911b6505b4b3636087b09a75bd12</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-01-26</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>עופר לוי &amp; הגר יפת - חיים של אמא</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>ינון אליה - סך הכל ילדה</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-01-26</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409366&amp;sid=eae9911b6505b4b3636087b09a75bd12</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-01-26</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>ינון אליה - סך הכל ילדה</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>טלשי - עצוב לי שככה</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-01-26</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409365&amp;sid=eae9911b6505b4b3636087b09a75bd12</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-01-26</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>טלשי - עצוב לי שככה</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>בצלאל שמיר - קרן אור</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-01-26</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409364&amp;sid=eae9911b6505b4b3636087b09a75bd12</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-01-26</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>בצלאל שמיר - קרן אור</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אודי שניידר - מתחת למים</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-01-26</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409363&amp;sid=eae9911b6505b4b3636087b09a75bd12</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-01-26</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אודי שניידר - מתחת למים</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>מאחורי הגב – חיפשתי אותך</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-01-26</v>
+      </c>
+      <c r="C10" t="str">
+        <v>https://yosmusic.com/%d7%9e%d7%90%d7%97%d7%95%d7%a8%d7%99-%d7%94%d7%92%d7%91-%d7%97%d7%99%d7%a4%d7%a9%d7%aa%d7%99-%d7%90%d7%95%d7%aa%d7%9a/</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-01-26</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v>"חיפשתי אותך" של שלישיית מאחורי הגב הוא שיר חיפוש קיומי, לירי ואינטימי, הבנוי כמנטרה רכה של תנועה מתמדת בין פנים לחוץ, בין אדם למקום, בין תשוקה לידיעה – ובין חוסר למציאה שלעולם אינה סופית. המילה "חיפשתי" חוזרת כמעט בכל שורה,</v>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>מאחורי הגב – חיפשתי אותך</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-01-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שימי לנגא - שיר תודה</v>
+        <v>אודי שניידר – מתחת למים</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409370&amp;sid=eae9911b6505b4b3636087b09a75bd12</v>
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%93%d7%99-%d7%a9%d7%a0%d7%99%d7%99%d7%93%d7%a8-%d7%9e%d7%aa%d7%97%d7%aa-%d7%9c%d7%9e%d7%99%d7%9d/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>אודי שניידר שר בלדה דרמטית רחבת נשימה, הנשענת על דימוי מרכזי חזק – המים כמטאפורה למצב נפשי של טשטוש, כמיהה ותלות רגשית. זהו שיר אהבה אך גם שיר על הישרדות, על נשימה בעולם שבו האהבה היא גם חמצן וגם סם.</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,316 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שימי לנגא - שיר תודה</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>רגב הוד - לירז</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-01-26</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409369&amp;sid=eae9911b6505b4b3636087b09a75bd12</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-01-26</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>רגב הוד - לירז</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>פן חזות - בואי</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-01-26</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409368&amp;sid=eae9911b6505b4b3636087b09a75bd12</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-01-26</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>פן חזות - בואי</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>עופר לוי &amp; הגר יפת - חיים של אמא</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-01-26</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409367&amp;sid=eae9911b6505b4b3636087b09a75bd12</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-01-26</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>עופר לוי &amp; הגר יפת - חיים של אמא</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>ינון אליה - סך הכל ילדה</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-01-26</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409366&amp;sid=eae9911b6505b4b3636087b09a75bd12</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-01-26</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>ינון אליה - סך הכל ילדה</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>טלשי - עצוב לי שככה</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-01-26</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409365&amp;sid=eae9911b6505b4b3636087b09a75bd12</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-01-26</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>טלשי - עצוב לי שככה</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>בצלאל שמיר - קרן אור</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-01-26</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409364&amp;sid=eae9911b6505b4b3636087b09a75bd12</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-01-26</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>בצלאל שמיר - קרן אור</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אודי שניידר - מתחת למים</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-01-26</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409363&amp;sid=eae9911b6505b4b3636087b09a75bd12</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-01-26</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אודי שניידר - מתחת למים</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>מאחורי הגב – חיפשתי אותך</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-01-26</v>
-      </c>
-      <c r="C10" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%90%d7%97%d7%95%d7%a8%d7%99-%d7%94%d7%92%d7%91-%d7%97%d7%99%d7%a4%d7%a9%d7%aa%d7%99-%d7%90%d7%95%d7%aa%d7%9a/</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-01-26</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v>"חיפשתי אותך" של שלישיית מאחורי הגב הוא שיר חיפוש קיומי, לירי ואינטימי, הבנוי כמנטרה רכה של תנועה מתמדת בין פנים לחוץ, בין אדם למקום, בין תשוקה לידיעה – ובין חוסר למציאה שלעולם אינה סופית. המילה "חיפשתי" חוזרת כמעט בכל שורה,</v>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>מאחורי הגב – חיפשתי אותך</v>
+        <v>אודי שניידר – מתחת למים</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-01-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-01-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אודי שניידר – מתחת למים</v>
+        <v>עמיר בניון – אות קין</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-27</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%95%d7%93%d7%99-%d7%a9%d7%a0%d7%99%d7%99%d7%93%d7%a8-%d7%9e%d7%aa%d7%97%d7%aa-%d7%9c%d7%9e%d7%99%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%a2%d7%9e%d7%99%d7%a8-%d7%91%d7%a0%d7%99%d7%95%d7%9f-%d7%90%d7%95%d7%aa-%d7%a7%d7%99%d7%9f/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-27</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>אודי שניידר שר בלדה דרמטית רחבת נשימה, הנשענת על דימוי מרכזי חזק – המים כמטאפורה למצב נפשי של טשטוש, כמיהה ותלות רגשית. זהו שיר אהבה אך גם שיר על הישרדות, על נשימה בעולם שבו האהבה היא גם חמצן וגם סם.</v>
+        <v>"אות קין" של עמיר בניון הוא אחד השירים החשופים, הקשים והעמוקים ברפרטואר שלו – יצירה שמתקיימת בו־זמנית כווידוי אישי, ככתב אישום עצמי, וכזעקה אנושית המבקשת מגע. זהו שיר שבו בניון משתמש בקולו הגבוה והמתפתל לא כאמצעי יופי בלבד, אלא ככלי</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אודי שניידר – מתחת למים</v>
+        <v>עמיר בניון – אות קין</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-01-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עמיר בניון – אות קין</v>
+        <v>נוי אביטל - מה מבקש להירפא הלילה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-27</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a2%d7%9e%d7%99%d7%a8-%d7%91%d7%a0%d7%99%d7%95%d7%9f-%d7%90%d7%95%d7%aa-%d7%a7%d7%99%d7%9f/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409379&amp;sid=0793a5f71c0836948f5e86de2cd6755d</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-27</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"אות קין" של עמיר בניון הוא אחד השירים החשופים, הקשים והעמוקים ברפרטואר שלו – יצירה שמתקיימת בו־זמנית כווידוי אישי, ככתב אישום עצמי, וכזעקה אנושית המבקשת מגע. זהו שיר שבו בניון משתמש בקולו הגבוה והמתפתל לא כאמצעי יופי בלבד, אלא ככלי</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,278 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עמיר בניון – אות קין</v>
+        <v>נוי אביטל - מה מבקש להירפא הלילה</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>יעל טאוב - קחי לך את הזמןת</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-01-27</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409378&amp;sid=0793a5f71c0836948f5e86de2cd6755d</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-01-27</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>יעל טאוב - קחי לך את הזמןת</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>ינון - להחזיק חזק</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-01-27</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409377&amp;sid=0793a5f71c0836948f5e86de2cd6755d</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-01-27</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>ינון - להחזיק חזק</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>גיל אוליאל - רק עוד רגע</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-01-27</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409376&amp;sid=0793a5f71c0836948f5e86de2cd6755d</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-01-27</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>גיל אוליאל - רק עוד רגע</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>בר סיידו - סיפור שנגמר</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-01-27</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409375&amp;sid=0793a5f71c0836948f5e86de2cd6755d</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-01-27</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>בר סיידו - סיפור שנגמר</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>בן שאשא &amp; שירה רווח - ניפגש במוצ''ש</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-01-27</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409373&amp;sid=0793a5f71c0836948f5e86de2cd6755d</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-01-27</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>בן שאשא &amp; שירה רווח - ניפגש במוצ''ש</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אדיר גץ - זירת אגרוף</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-01-27</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409372&amp;sid=0793a5f71c0836948f5e86de2cd6755d</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-01-27</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אדיר גץ - זירת אגרוף</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אגם איזן - תעשי אהבה</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-01-27</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409371&amp;sid=0793a5f71c0836948f5e86de2cd6755d</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-01-27</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אגם איזן - תעשי אהבה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-01-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נוי אביטל - מה מבקש להירפא הלילה</v>
+        <v>שיר דוד גדסי - הִתְנַעַרְתִּי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-27</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409379&amp;sid=0793a5f71c0836948f5e86de2cd6755d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409384&amp;sid=aaae679c63a0fb8b7ff9fe33cb51fcb2</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-27</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נוי אביטל - מה מבקש להירפא הלילה</v>
+        <v>שיר דוד גדסי - הִתְנַעַרְתִּי</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>יעל טאוב - קחי לך את הזמןת</v>
+        <v>עקיבא הירש פמנסקי - מחרוזת חתונות 2026</v>
       </c>
       <c r="B3" t="str">
         <v>2026-01-27</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409378&amp;sid=0793a5f71c0836948f5e86de2cd6755d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409383&amp;sid=aaae679c63a0fb8b7ff9fe33cb51fcb2</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-27</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>יעל טאוב - קחי לך את הזמןת</v>
+        <v>עקיבא הירש פמנסקי - מחרוזת חתונות 2026</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ינון - להחזיק חזק</v>
+        <v>עמיר בניון - אות קין</v>
       </c>
       <c r="B4" t="str">
         <v>2026-01-27</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409377&amp;sid=0793a5f71c0836948f5e86de2cd6755d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409382&amp;sid=aaae679c63a0fb8b7ff9fe33cb51fcb2</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-27</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>ינון - להחזיק חזק</v>
+        <v>עמיר בניון - אות קין</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>גיל אוליאל - רק עוד רגע</v>
+        <v>עידן בקשי - נשיקות ושתיקות</v>
       </c>
       <c r="B5" t="str">
         <v>2026-01-27</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409376&amp;sid=0793a5f71c0836948f5e86de2cd6755d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409381&amp;sid=aaae679c63a0fb8b7ff9fe33cb51fcb2</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-27</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>גיל אוליאל - רק עוד רגע</v>
+        <v>עידן בקשי - נשיקות ושתיקות</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>בר סיידו - סיפור שנגמר</v>
+        <v>ניר אליאב - שבועיים בנפרד</v>
       </c>
       <c r="B6" t="str">
         <v>2026-01-27</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409375&amp;sid=0793a5f71c0836948f5e86de2cd6755d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409380&amp;sid=aaae679c63a0fb8b7ff9fe33cb51fcb2</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-27</v>
@@ -621,126 +621,12 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>בר סיידו - סיפור שנגמר</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>בן שאשא &amp; שירה רווח - ניפגש במוצ''ש</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-01-27</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409373&amp;sid=0793a5f71c0836948f5e86de2cd6755d</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-01-27</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>בן שאשא &amp; שירה רווח - ניפגש במוצ''ש</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>אדיר גץ - זירת אגרוף</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-01-27</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409372&amp;sid=0793a5f71c0836948f5e86de2cd6755d</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-01-27</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>אדיר גץ - זירת אגרוף</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אגם איזן - תעשי אהבה</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-01-27</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409371&amp;sid=0793a5f71c0836948f5e86de2cd6755d</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-01-27</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אגם איזן - תעשי אהבה</v>
+        <v>ניר אליאב - שבועיים בנפרד</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-01-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שיר דוד גדסי - הִתְנַעַרְתִּי</v>
+        <v>זוהר בנאי – גם אם לא נתראה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409384&amp;sid=aaae679c63a0fb8b7ff9fe33cb51fcb2</v>
+        <v>https://yosmusic.com/%d7%96%d7%95%d7%94%d7%a8-%d7%91%d7%a0%d7%90%d7%99-%d7%92%d7%9d-%d7%90%d7%9d-%d7%9c%d7%90-%d7%a0%d7%aa%d7%a8%d7%90%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-27</v>
+        <v>2026-01-28</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>השיר "גם אם לא נתראה" ששרה זוהר בנאי הוא יצירה עדינה, אינטימית ומרוסנת, שמדברת על קשר אנושי שאינו תלוי בנוכחות פיזית או בהבטחות גדולות – אלא בעצם הידיעה שמישהו קיים עבורך. זהו שיר על קרבה שקטה, על בית רגשי, ועל</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,164 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שיר דוד גדסי - הִתְנַעַרְתִּי</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>עקיבא הירש פמנסקי - מחרוזת חתונות 2026</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-01-27</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409383&amp;sid=aaae679c63a0fb8b7ff9fe33cb51fcb2</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-01-27</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>עקיבא הירש פמנסקי - מחרוזת חתונות 2026</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>עמיר בניון - אות קין</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-01-27</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409382&amp;sid=aaae679c63a0fb8b7ff9fe33cb51fcb2</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-01-27</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>עמיר בניון - אות קין</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>עידן בקשי - נשיקות ושתיקות</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-01-27</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409381&amp;sid=aaae679c63a0fb8b7ff9fe33cb51fcb2</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-01-27</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>עידן בקשי - נשיקות ושתיקות</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>ניר אליאב - שבועיים בנפרד</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-01-27</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409380&amp;sid=aaae679c63a0fb8b7ff9fe33cb51fcb2</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-01-27</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>ניר אליאב - שבועיים בנפרד</v>
+        <v>זוהר בנאי – גם אם לא נתראה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>